--- a/research/traditional_assets/database/data/monaco/monaco_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/monaco/monaco_hotel_gaming.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07819047427270967</v>
+        <v>0.07803060680669288</v>
       </c>
       <c r="C2">
-        <v>2611.689145967125</v>
+        <v>2597.335660965596</v>
       </c>
       <c r="D2">
-        <v>2405.089145967125</v>
+        <v>2417.018660965596</v>
       </c>
       <c r="E2">
-        <v>-39.3</v>
+        <v>-13.017</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.283</v>
       </c>
       <c r="G2">
         <v>206.6</v>
@@ -1451,28 +1451,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3220349</v>
       </c>
       <c r="N2">
-        <v>83.60000000000001</v>
+        <v>82.2779651</v>
       </c>
       <c r="O2">
-        <v>20.71208359806992</v>
+        <v>20.38454654820908</v>
       </c>
       <c r="P2">
-        <v>62.88791640193008</v>
+        <v>61.89341855179092</v>
       </c>
       <c r="Q2">
-        <v>153.5879164019301</v>
+        <v>152.5934185517909</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07819047427270967</v>
+        <v>0.07843659208217768</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7537319187569904</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>63.23584952258069</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07803060680669288</v>
+        <v>0.07787073934067609</v>
       </c>
       <c r="C3">
-        <v>2597.335660965596</v>
+        <v>2583.101109382679</v>
       </c>
       <c r="D3">
-        <v>2417.018660965596</v>
+        <v>2429.067109382679</v>
       </c>
       <c r="E3">
-        <v>-13.017</v>
+        <v>13.26600000000001</v>
       </c>
       <c r="F3">
-        <v>26.283</v>
+        <v>52.566</v>
       </c>
       <c r="G3">
         <v>206.6</v>
@@ -1533,28 +1533,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M3">
-        <v>1.3220349</v>
+        <v>2.6440698</v>
       </c>
       <c r="N3">
-        <v>82.2779651</v>
+        <v>80.95593020000001</v>
       </c>
       <c r="O3">
-        <v>20.38454654820908</v>
+        <v>20.05700949834825</v>
       </c>
       <c r="P3">
-        <v>61.89341855179092</v>
+        <v>60.89892070165176</v>
       </c>
       <c r="Q3">
-        <v>152.5934185517909</v>
+        <v>151.5989207016518</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07843659208217768</v>
+        <v>0.07868773270408383</v>
       </c>
       <c r="T3">
-        <v>0.7537319187569904</v>
+        <v>0.7595319331197188</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>63.23584952258069</v>
+        <v>31.61792476129035</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07787073934067609</v>
+        <v>0.07771087187465929</v>
       </c>
       <c r="C4">
-        <v>2583.101109382679</v>
+        <v>2568.987278720548</v>
       </c>
       <c r="D4">
-        <v>2429.067109382679</v>
+        <v>2441.236278720548</v>
       </c>
       <c r="E4">
-        <v>13.26600000000001</v>
+        <v>39.54900000000001</v>
       </c>
       <c r="F4">
-        <v>52.566</v>
+        <v>78.849</v>
       </c>
       <c r="G4">
         <v>206.6</v>
@@ -1615,28 +1615,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M4">
-        <v>2.6440698</v>
+        <v>3.9661047</v>
       </c>
       <c r="N4">
-        <v>80.95593020000001</v>
+        <v>79.63389530000001</v>
       </c>
       <c r="O4">
-        <v>20.05700949834825</v>
+        <v>19.72947244848741</v>
       </c>
       <c r="P4">
-        <v>60.89892070165176</v>
+        <v>59.90442285151259</v>
       </c>
       <c r="Q4">
-        <v>151.5989207016518</v>
+        <v>150.6044228515126</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07868773270408383</v>
+        <v>0.07894405148314265</v>
       </c>
       <c r="T4">
-        <v>0.7595319331197188</v>
+        <v>0.7654515354074517</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.61792476129035</v>
+        <v>21.0786165075269</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07771087187465929</v>
+        <v>0.0775510044086425</v>
       </c>
       <c r="C5">
-        <v>2568.987278720548</v>
+        <v>2554.995992481927</v>
       </c>
       <c r="D5">
-        <v>2441.236278720548</v>
+        <v>2453.527992481927</v>
       </c>
       <c r="E5">
-        <v>39.54900000000001</v>
+        <v>65.83200000000001</v>
       </c>
       <c r="F5">
-        <v>78.849</v>
+        <v>105.132</v>
       </c>
       <c r="G5">
         <v>206.6</v>
@@ -1697,28 +1697,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M5">
-        <v>3.9661047</v>
+        <v>5.2881396</v>
       </c>
       <c r="N5">
-        <v>79.63389530000001</v>
+        <v>78.31186040000001</v>
       </c>
       <c r="O5">
-        <v>19.72947244848741</v>
+        <v>19.40193539862657</v>
       </c>
       <c r="P5">
-        <v>59.90442285151259</v>
+        <v>58.90992500137344</v>
       </c>
       <c r="Q5">
-        <v>150.6044228515126</v>
+        <v>149.6099250013734</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07894405148314265</v>
+        <v>0.07920571023676522</v>
       </c>
       <c r="T5">
-        <v>0.7654515354074517</v>
+        <v>0.7714944627428457</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.0786165075269</v>
+        <v>15.80896238064517</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0775510044086425</v>
+        <v>0.07744755552791451</v>
       </c>
       <c r="C6">
-        <v>2554.995992481927</v>
+        <v>2536.733034485904</v>
       </c>
       <c r="D6">
-        <v>2453.527992481927</v>
+        <v>2461.548034485904</v>
       </c>
       <c r="E6">
-        <v>65.83200000000001</v>
+        <v>92.11500000000002</v>
       </c>
       <c r="F6">
-        <v>105.132</v>
+        <v>131.415</v>
       </c>
       <c r="G6">
         <v>206.6</v>
@@ -1779,45 +1779,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M6">
-        <v>5.2881396</v>
+        <v>6.807297000000001</v>
       </c>
       <c r="N6">
-        <v>78.31186040000001</v>
+        <v>76.792703</v>
       </c>
       <c r="O6">
-        <v>19.40193539862657</v>
+        <v>19.02556081648032</v>
       </c>
       <c r="P6">
-        <v>58.90992500137344</v>
+        <v>57.76714218351968</v>
       </c>
       <c r="Q6">
-        <v>149.6099250013734</v>
+        <v>148.4671421835197</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07920571023676522</v>
+        <v>0.0794728775957272</v>
       </c>
       <c r="T6">
-        <v>0.7714944627428457</v>
+        <v>0.7776646096010901</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2477521961491617</v>
       </c>
       <c r="W6">
-        <v>0.03783806453369716</v>
+        <v>0.03896643623947342</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.80896238064517</v>
+        <v>12.28093911577532</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07744755552791451</v>
+        <v>0.07729897177895549</v>
       </c>
       <c r="C7">
-        <v>2536.733034485904</v>
+        <v>2522.061398747989</v>
       </c>
       <c r="D7">
-        <v>2461.548034485904</v>
+        <v>2473.159398747989</v>
       </c>
       <c r="E7">
-        <v>92.11500000000002</v>
+        <v>118.398</v>
       </c>
       <c r="F7">
-        <v>131.415</v>
+        <v>157.698</v>
       </c>
       <c r="G7">
         <v>206.6</v>
@@ -1861,28 +1861,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M7">
-        <v>6.807297000000001</v>
+        <v>8.168756400000001</v>
       </c>
       <c r="N7">
-        <v>76.792703</v>
+        <v>75.4312436</v>
       </c>
       <c r="O7">
-        <v>19.02556081648032</v>
+        <v>18.6882562601624</v>
       </c>
       <c r="P7">
-        <v>57.76714218351968</v>
+        <v>56.7429873398376</v>
       </c>
       <c r="Q7">
-        <v>148.4671421835197</v>
+        <v>147.4429873398376</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0794728775957272</v>
+        <v>0.079745729366582</v>
       </c>
       <c r="T7">
-        <v>0.7776646096010901</v>
+        <v>0.7839660361797227</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.28093911577532</v>
+        <v>10.23411592981277</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07729897177895549</v>
+        <v>0.07723990551865469</v>
       </c>
       <c r="C8">
-        <v>2522.061398747989</v>
+        <v>2500.424731947851</v>
       </c>
       <c r="D8">
-        <v>2473.159398747989</v>
+        <v>2477.805731947851</v>
       </c>
       <c r="E8">
-        <v>118.398</v>
+        <v>144.681</v>
       </c>
       <c r="F8">
-        <v>157.698</v>
+        <v>183.981</v>
       </c>
       <c r="G8">
         <v>206.6</v>
@@ -1943,45 +1943,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M8">
-        <v>8.168756399999999</v>
+        <v>9.842983499999999</v>
       </c>
       <c r="N8">
-        <v>75.43124360000002</v>
+        <v>73.75701650000001</v>
       </c>
       <c r="O8">
-        <v>18.6882562601624</v>
+        <v>18.27346281928496</v>
       </c>
       <c r="P8">
-        <v>56.74298733983761</v>
+        <v>55.48355368071505</v>
       </c>
       <c r="Q8">
-        <v>147.4429873398376</v>
+        <v>146.1835536807151</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.079745729366582</v>
+        <v>0.08002444891745517</v>
       </c>
       <c r="T8">
-        <v>0.7839660361797227</v>
+        <v>0.7904029773084333</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2477521961491617</v>
       </c>
       <c r="W8">
-        <v>0.03896643623947342</v>
+        <v>0.04024525750601984</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.23411592981277</v>
+        <v>8.493359762311906</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0772399055186547</v>
+        <v>0.07715225384180759</v>
       </c>
       <c r="C9">
-        <v>2500.42473194785</v>
+        <v>2481.068947720038</v>
       </c>
       <c r="D9">
-        <v>2477.80573194785</v>
+        <v>2484.732947720038</v>
       </c>
       <c r="E9">
-        <v>144.681</v>
+        <v>170.964</v>
       </c>
       <c r="F9">
-        <v>183.981</v>
+        <v>210.264</v>
       </c>
       <c r="G9">
         <v>206.6</v>
@@ -2025,45 +2025,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M9">
-        <v>9.842983500000001</v>
+        <v>11.4173352</v>
       </c>
       <c r="N9">
-        <v>73.75701650000001</v>
+        <v>72.18266480000001</v>
       </c>
       <c r="O9">
-        <v>18.27346281928496</v>
+        <v>17.88341372809879</v>
       </c>
       <c r="P9">
-        <v>55.48355368071505</v>
+        <v>54.29925107190122</v>
       </c>
       <c r="Q9">
-        <v>146.1835536807151</v>
+        <v>144.9992510719012</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08002444891745517</v>
+        <v>0.0803092275889995</v>
       </c>
       <c r="T9">
-        <v>0.7904029773084333</v>
+        <v>0.7969798519399423</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.2477521961491617</v>
       </c>
       <c r="W9">
-        <v>0.04024525750601984</v>
+        <v>0.04084705574910052</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.493359762311904</v>
+        <v>7.322198966357755</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07715225384180759</v>
+        <v>0.07702247628794481</v>
       </c>
       <c r="C10">
-        <v>2481.068947720038</v>
+        <v>2465.113846153957</v>
       </c>
       <c r="D10">
-        <v>2484.732947720038</v>
+        <v>2495.060846153957</v>
       </c>
       <c r="E10">
-        <v>170.964</v>
+        <v>197.247</v>
       </c>
       <c r="F10">
-        <v>210.264</v>
+        <v>236.547</v>
       </c>
       <c r="G10">
         <v>206.6</v>
@@ -2107,28 +2107,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M10">
-        <v>11.4173352</v>
+        <v>12.8445021</v>
       </c>
       <c r="N10">
-        <v>72.18266480000001</v>
+        <v>70.75549790000001</v>
       </c>
       <c r="O10">
-        <v>17.88341372809879</v>
+        <v>17.5298299943524</v>
       </c>
       <c r="P10">
-        <v>54.29925107190122</v>
+        <v>53.22566790564761</v>
       </c>
       <c r="Q10">
-        <v>144.9992510719012</v>
+        <v>143.9256679056476</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0803092275889995</v>
+        <v>0.08060026513244589</v>
       </c>
       <c r="T10">
-        <v>0.7969798519399423</v>
+        <v>0.803701273266649</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.322198966357755</v>
+        <v>6.508621303429115</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07702247628794481</v>
+        <v>0.07696792351446714</v>
       </c>
       <c r="C11">
-        <v>2465.113846153957</v>
+        <v>2443.197915685877</v>
       </c>
       <c r="D11">
-        <v>2495.060846153957</v>
+        <v>2499.427915685877</v>
       </c>
       <c r="E11">
-        <v>197.247</v>
+        <v>223.53</v>
       </c>
       <c r="F11">
-        <v>236.547</v>
+        <v>262.83</v>
       </c>
       <c r="G11">
         <v>206.6</v>
@@ -2189,45 +2189,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M11">
-        <v>12.8445021</v>
+        <v>14.534499</v>
       </c>
       <c r="N11">
-        <v>70.75549790000001</v>
+        <v>69.06550100000001</v>
       </c>
       <c r="O11">
-        <v>17.5298299943524</v>
+        <v>17.11112955089213</v>
       </c>
       <c r="P11">
-        <v>53.22566790564761</v>
+        <v>51.95437144910788</v>
       </c>
       <c r="Q11">
-        <v>143.9256679056476</v>
+        <v>142.6543714491079</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08060026513244589</v>
+        <v>0.08089777017685779</v>
       </c>
       <c r="T11">
-        <v>0.803701273266649</v>
+        <v>0.8105720595117271</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.2477521961491617</v>
       </c>
       <c r="W11">
-        <v>0.04084705574910052</v>
+        <v>0.04159930355295136</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.508621303429115</v>
+        <v>5.751832244097304</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07696792351446714</v>
+        <v>0.07684566843864288</v>
       </c>
       <c r="C12">
-        <v>2443.197915685877</v>
+        <v>2426.757440093215</v>
       </c>
       <c r="D12">
-        <v>2499.427915685877</v>
+        <v>2509.270440093215</v>
       </c>
       <c r="E12">
-        <v>223.53</v>
+        <v>249.813</v>
       </c>
       <c r="F12">
-        <v>262.83</v>
+        <v>289.113</v>
       </c>
       <c r="G12">
         <v>206.6</v>
@@ -2271,28 +2271,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M12">
-        <v>14.534499</v>
+        <v>15.9879489</v>
       </c>
       <c r="N12">
-        <v>69.06550100000001</v>
+        <v>67.6120511</v>
       </c>
       <c r="O12">
-        <v>17.11112955089213</v>
+        <v>16.75103414617434</v>
       </c>
       <c r="P12">
-        <v>51.95437144910788</v>
+        <v>50.86101695382565</v>
       </c>
       <c r="Q12">
-        <v>142.6543714491079</v>
+        <v>141.5610169538257</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08089777017685779</v>
+        <v>0.08120196072788566</v>
       </c>
       <c r="T12">
-        <v>0.8105720595117271</v>
+        <v>0.8175972454477058</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.751832244097303</v>
+        <v>5.22893840372482</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07684566843864288</v>
+        <v>0.07672341336281863</v>
       </c>
       <c r="C13">
-        <v>2426.757440093215</v>
+        <v>2410.394788934329</v>
       </c>
       <c r="D13">
-        <v>2509.270440093215</v>
+        <v>2519.190788934329</v>
       </c>
       <c r="E13">
-        <v>249.813</v>
+        <v>276.096</v>
       </c>
       <c r="F13">
-        <v>289.113</v>
+        <v>315.396</v>
       </c>
       <c r="G13">
         <v>206.6</v>
@@ -2353,28 +2353,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M13">
-        <v>15.9879489</v>
+        <v>17.4413988</v>
       </c>
       <c r="N13">
-        <v>67.6120511</v>
+        <v>66.15860120000001</v>
       </c>
       <c r="O13">
-        <v>16.75103414617434</v>
+        <v>16.39093874145657</v>
       </c>
       <c r="P13">
-        <v>50.86101695382565</v>
+        <v>49.76766245854344</v>
       </c>
       <c r="Q13">
-        <v>141.5610169538257</v>
+        <v>140.4676624585434</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08120196072788566</v>
+        <v>0.0815130647005278</v>
       </c>
       <c r="T13">
-        <v>0.8175972454477058</v>
+        <v>0.8247820947004112</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.22893840372482</v>
+        <v>4.793193536747753</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07672341336281863</v>
+        <v>0.07684563882324588</v>
       </c>
       <c r="C14">
-        <v>2410.394788934329</v>
+        <v>2374.193833764051</v>
       </c>
       <c r="D14">
-        <v>2519.190788934329</v>
+        <v>2509.272833764051</v>
       </c>
       <c r="E14">
-        <v>276.096</v>
+        <v>302.379</v>
       </c>
       <c r="F14">
-        <v>315.396</v>
+        <v>341.679</v>
       </c>
       <c r="G14">
         <v>206.6</v>
@@ -2435,45 +2435,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M14">
-        <v>17.4413988</v>
+        <v>19.7490462</v>
       </c>
       <c r="N14">
-        <v>66.15860120000001</v>
+        <v>63.85095380000001</v>
       </c>
       <c r="O14">
-        <v>16.39093874145657</v>
+        <v>15.81921403016866</v>
       </c>
       <c r="P14">
-        <v>49.76766245854344</v>
+        <v>48.03173976983134</v>
       </c>
       <c r="Q14">
-        <v>140.4676624585434</v>
+        <v>138.7317397698313</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0815130647005278</v>
+        <v>0.08183132048863298</v>
       </c>
       <c r="T14">
-        <v>0.8247820947004112</v>
+        <v>0.8321321129014547</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.2477521961491617</v>
       </c>
       <c r="W14">
-        <v>0.04159930355295136</v>
+        <v>0.04347992306257845</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.793193536747753</v>
+        <v>4.233115825107544</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07684563882324588</v>
+        <v>0.07711079136640484</v>
       </c>
       <c r="C15">
-        <v>2374.193833764051</v>
+        <v>2326.661288661014</v>
       </c>
       <c r="D15">
-        <v>2509.272833764051</v>
+        <v>2488.023288661014</v>
       </c>
       <c r="E15">
-        <v>302.379</v>
+        <v>328.662</v>
       </c>
       <c r="F15">
-        <v>341.679</v>
+        <v>367.962</v>
       </c>
       <c r="G15">
         <v>206.6</v>
@@ -2517,45 +2517,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M15">
-        <v>19.7490462</v>
+        <v>22.5560706</v>
       </c>
       <c r="N15">
-        <v>63.85095380000001</v>
+        <v>61.04392940000001</v>
       </c>
       <c r="O15">
-        <v>15.81921403016866</v>
+        <v>15.12376757042438</v>
       </c>
       <c r="P15">
-        <v>48.03173976983134</v>
+        <v>45.92016182957563</v>
       </c>
       <c r="Q15">
-        <v>138.7317397698313</v>
+        <v>136.6201618295756</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08183132048863298</v>
+        <v>0.08215697757413598</v>
       </c>
       <c r="T15">
-        <v>0.8321321129014547</v>
+        <v>0.8396530617583365</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.2477521961491617</v>
       </c>
       <c r="W15">
-        <v>0.04347992306257845</v>
+        <v>0.04611279037605638</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.233115825107544</v>
+        <v>3.70631930900234</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07711079136640484</v>
+        <v>0.07734961523642897</v>
       </c>
       <c r="C16">
-        <v>2326.661288661014</v>
+        <v>2281.544482097754</v>
       </c>
       <c r="D16">
-        <v>2488.023288661014</v>
+        <v>2469.189482097754</v>
       </c>
       <c r="E16">
-        <v>328.662</v>
+        <v>354.9450000000001</v>
       </c>
       <c r="F16">
-        <v>367.962</v>
+        <v>394.2450000000001</v>
       </c>
       <c r="G16">
         <v>206.6</v>
@@ -2599,45 +2599,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M16">
-        <v>22.5560706</v>
+        <v>25.27110450000001</v>
       </c>
       <c r="N16">
-        <v>61.04392940000001</v>
+        <v>58.3288955</v>
       </c>
       <c r="O16">
-        <v>15.12376757042438</v>
+        <v>14.45111195907996</v>
       </c>
       <c r="P16">
-        <v>45.92016182957563</v>
+        <v>43.87778354092005</v>
       </c>
       <c r="Q16">
-        <v>136.6201618295756</v>
+        <v>134.5777835409201</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08215697757413598</v>
+        <v>0.08249029717929784</v>
       </c>
       <c r="T16">
-        <v>0.8396530617583365</v>
+        <v>0.8473509741177331</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.2477521961491617</v>
       </c>
       <c r="W16">
-        <v>0.04611279037605638</v>
+        <v>0.04821908422683873</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.70631930900234</v>
+        <v>3.308126085268651</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07734961523642897</v>
+        <v>0.07729355796734359</v>
       </c>
       <c r="C17">
-        <v>2281.544482097754</v>
+        <v>2259.656540266928</v>
       </c>
       <c r="D17">
-        <v>2469.189482097754</v>
+        <v>2473.584540266928</v>
       </c>
       <c r="E17">
-        <v>354.945</v>
+        <v>381.228</v>
       </c>
       <c r="F17">
-        <v>394.245</v>
+        <v>420.528</v>
       </c>
       <c r="G17">
         <v>206.6</v>
@@ -2681,28 +2681,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M17">
-        <v>25.2711045</v>
+        <v>26.9558448</v>
       </c>
       <c r="N17">
-        <v>58.3288955</v>
+        <v>56.64415520000001</v>
       </c>
       <c r="O17">
-        <v>14.45111195907996</v>
+        <v>14.03371384981396</v>
       </c>
       <c r="P17">
-        <v>43.87778354092005</v>
+        <v>42.61044135018605</v>
       </c>
       <c r="Q17">
-        <v>134.5777835409201</v>
+        <v>133.3104413501861</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08249029717929784</v>
+        <v>0.082831552965535</v>
       </c>
       <c r="T17">
-        <v>0.8473509741177331</v>
+        <v>0.8552321701047344</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.308126085268651</v>
+        <v>3.101368204939361</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07729355796734359</v>
+        <v>0.07823498128616443</v>
       </c>
       <c r="C18">
-        <v>2259.656540266928</v>
+        <v>2161.577902503593</v>
       </c>
       <c r="D18">
-        <v>2473.584540266928</v>
+        <v>2401.788902503593</v>
       </c>
       <c r="E18">
-        <v>381.228</v>
+        <v>407.511</v>
       </c>
       <c r="F18">
-        <v>420.528</v>
+        <v>446.811</v>
       </c>
       <c r="G18">
         <v>206.6</v>
@@ -2763,45 +2763,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M18">
-        <v>26.9558448</v>
+        <v>32.12571090000001</v>
       </c>
       <c r="N18">
-        <v>56.64415520000001</v>
+        <v>51.4742891</v>
       </c>
       <c r="O18">
-        <v>14.03371384981396</v>
+        <v>12.75286816974186</v>
       </c>
       <c r="P18">
-        <v>42.61044135018605</v>
+        <v>38.72142093025814</v>
       </c>
       <c r="Q18">
-        <v>133.3104413501861</v>
+        <v>129.4214209302581</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.082831552965535</v>
+        <v>0.08318103178276583</v>
       </c>
       <c r="T18">
-        <v>0.8552321701047344</v>
+        <v>0.863303274428772</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.2477521961491617</v>
       </c>
       <c r="W18">
-        <v>0.04821908422683873</v>
+        <v>0.05408661709687528</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.101368204939361</v>
+        <v>2.602277044085583</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07823498128616443</v>
+        <v>0.0787656773040827</v>
       </c>
       <c r="C19">
-        <v>2161.577902503593</v>
+        <v>2096.629845065775</v>
       </c>
       <c r="D19">
-        <v>2401.788902503593</v>
+        <v>2363.123845065775</v>
       </c>
       <c r="E19">
-        <v>407.511</v>
+        <v>433.7940000000001</v>
       </c>
       <c r="F19">
-        <v>446.811</v>
+        <v>473.0940000000001</v>
       </c>
       <c r="G19">
         <v>206.6</v>
@@ -2845,45 +2845,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M19">
-        <v>32.12571090000001</v>
+        <v>35.86052520000001</v>
       </c>
       <c r="N19">
-        <v>51.4742891</v>
+        <v>47.7394748</v>
       </c>
       <c r="O19">
-        <v>12.75286816974186</v>
+        <v>11.82755972470756</v>
       </c>
       <c r="P19">
-        <v>38.72142093025814</v>
+        <v>35.91191507529243</v>
       </c>
       <c r="Q19">
-        <v>129.4214209302581</v>
+        <v>126.6119150752924</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08318103178276583</v>
+        <v>0.08353903447358763</v>
       </c>
       <c r="T19">
-        <v>0.863303274428772</v>
+        <v>0.8715712349558346</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.2477521961491617</v>
       </c>
       <c r="W19">
-        <v>0.05408661709687528</v>
+        <v>0.05702038353189354</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.602277044085583</v>
+        <v>2.331254200370718</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07876567730408268</v>
+        <v>0.07879763302804788</v>
       </c>
       <c r="C20">
-        <v>2096.629845065776</v>
+        <v>2068.058337486329</v>
       </c>
       <c r="D20">
-        <v>2363.123845065776</v>
+        <v>2360.835337486329</v>
       </c>
       <c r="E20">
-        <v>433.794</v>
+        <v>460.0770000000001</v>
       </c>
       <c r="F20">
-        <v>473.094</v>
+        <v>499.3770000000001</v>
       </c>
       <c r="G20">
         <v>206.6</v>
@@ -2927,28 +2927,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M20">
-        <v>35.8605252</v>
+        <v>37.85277660000001</v>
       </c>
       <c r="N20">
-        <v>47.7394748</v>
+        <v>45.7472234</v>
       </c>
       <c r="O20">
-        <v>11.82755972470756</v>
+        <v>11.33397506507632</v>
       </c>
       <c r="P20">
-        <v>35.91191507529244</v>
+        <v>34.41324833492368</v>
       </c>
       <c r="Q20">
-        <v>126.6119150752924</v>
+        <v>125.1132483349237</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08353903447358763</v>
+        <v>0.08390587673702234</v>
       </c>
       <c r="T20">
-        <v>0.8715712349558346</v>
+        <v>0.880043342656405</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.331254200370719</v>
+        <v>2.208556610877523</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07879763302804788</v>
+        <v>0.07882958875201304</v>
       </c>
       <c r="C21">
-        <v>2068.058337486329</v>
+        <v>2039.491258113184</v>
       </c>
       <c r="D21">
-        <v>2360.835337486329</v>
+        <v>2358.551258113184</v>
       </c>
       <c r="E21">
-        <v>460.0770000000001</v>
+        <v>486.3600000000001</v>
       </c>
       <c r="F21">
-        <v>499.3770000000001</v>
+        <v>525.6600000000001</v>
       </c>
       <c r="G21">
         <v>206.6</v>
@@ -3009,28 +3009,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M21">
-        <v>37.85277660000001</v>
+        <v>39.84502800000001</v>
       </c>
       <c r="N21">
-        <v>45.7472234</v>
+        <v>43.754972</v>
       </c>
       <c r="O21">
-        <v>11.33397506507632</v>
+        <v>10.84039040544508</v>
       </c>
       <c r="P21">
-        <v>34.41324833492368</v>
+        <v>32.91458159455492</v>
       </c>
       <c r="Q21">
-        <v>125.1132483349237</v>
+        <v>123.6145815945549</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08390587673702234</v>
+        <v>0.08428189005704291</v>
       </c>
       <c r="T21">
-        <v>0.880043342656405</v>
+        <v>0.8887272530494899</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.208556610877523</v>
+        <v>2.098128780333647</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07882958875201304</v>
+        <v>0.08110474742706142</v>
       </c>
       <c r="C22">
-        <v>2039.491258113184</v>
+        <v>1861.215148219716</v>
       </c>
       <c r="D22">
-        <v>2358.551258113184</v>
+        <v>2206.558148219717</v>
       </c>
       <c r="E22">
-        <v>486.3600000000001</v>
+        <v>512.6430000000001</v>
       </c>
       <c r="F22">
-        <v>525.6600000000001</v>
+        <v>551.9430000000001</v>
       </c>
       <c r="G22">
         <v>206.6</v>
@@ -3091,45 +3091,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M22">
-        <v>39.84502800000001</v>
+        <v>49.67487000000001</v>
       </c>
       <c r="N22">
-        <v>43.754972</v>
+        <v>33.92513</v>
       </c>
       <c r="O22">
-        <v>10.84039040544508</v>
+        <v>8.405025462145812</v>
       </c>
       <c r="P22">
-        <v>32.91458159455492</v>
+        <v>25.52010453785419</v>
       </c>
       <c r="Q22">
-        <v>123.6145815945549</v>
+        <v>116.2201045378542</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08428189005704291</v>
+        <v>0.08466742270162098</v>
       </c>
       <c r="T22">
-        <v>0.8887272530494899</v>
+        <v>0.897631009275311</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.2477521961491617</v>
       </c>
       <c r="W22">
-        <v>0.05702038353189354</v>
+        <v>0.06770230234657544</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.098128780333647</v>
+        <v>1.682943508458099</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08110474742706142</v>
+        <v>0.0812435223391734</v>
       </c>
       <c r="C23">
-        <v>1861.215148219717</v>
+        <v>1826.292631239466</v>
       </c>
       <c r="D23">
-        <v>2206.558148219717</v>
+        <v>2197.918631239466</v>
       </c>
       <c r="E23">
-        <v>512.643</v>
+        <v>538.926</v>
       </c>
       <c r="F23">
-        <v>551.943</v>
+        <v>578.226</v>
       </c>
       <c r="G23">
         <v>206.6</v>
@@ -3173,28 +3173,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M23">
-        <v>49.67487</v>
+        <v>52.04034</v>
       </c>
       <c r="N23">
-        <v>33.92513000000001</v>
+        <v>31.55966000000001</v>
       </c>
       <c r="O23">
-        <v>8.405025462145813</v>
+        <v>7.818975074720855</v>
       </c>
       <c r="P23">
-        <v>25.52010453785419</v>
+        <v>23.74068492527915</v>
       </c>
       <c r="Q23">
-        <v>116.2201045378542</v>
+        <v>114.4406849252792</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08466742270162098</v>
+        <v>0.0850628407986241</v>
       </c>
       <c r="T23">
-        <v>0.897631009275311</v>
+        <v>0.9067630669428198</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.6829435084581</v>
+        <v>1.606446076255459</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0812435223391734</v>
+        <v>0.08138229725128537</v>
       </c>
       <c r="C24">
-        <v>1826.292631239466</v>
+        <v>1791.437504411188</v>
       </c>
       <c r="D24">
-        <v>2197.918631239466</v>
+        <v>2189.346504411188</v>
       </c>
       <c r="E24">
-        <v>538.926</v>
+        <v>565.2090000000001</v>
       </c>
       <c r="F24">
-        <v>578.226</v>
+        <v>604.509</v>
       </c>
       <c r="G24">
         <v>206.6</v>
@@ -3255,28 +3255,28 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M24">
-        <v>52.04034</v>
+        <v>54.40581</v>
       </c>
       <c r="N24">
-        <v>31.55966000000001</v>
+        <v>29.19419000000001</v>
       </c>
       <c r="O24">
-        <v>7.818975074720855</v>
+        <v>7.232924687295897</v>
       </c>
       <c r="P24">
-        <v>23.74068492527915</v>
+        <v>21.96126531270411</v>
       </c>
       <c r="Q24">
-        <v>114.4406849252792</v>
+        <v>112.6612653127041</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0850628407986241</v>
+        <v>0.08546852949554939</v>
       </c>
       <c r="T24">
-        <v>0.9067630669428198</v>
+        <v>0.9161323209133808</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.606446076255459</v>
+        <v>1.536600594679135</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08138229725128537</v>
+        <v>0.0928113016474921</v>
       </c>
       <c r="C25">
-        <v>1791.437504411188</v>
+        <v>1232.898430938477</v>
       </c>
       <c r="D25">
-        <v>2189.346504411188</v>
+        <v>1657.090430938478</v>
       </c>
       <c r="E25">
-        <v>565.2090000000001</v>
+        <v>591.4920000000002</v>
       </c>
       <c r="F25">
-        <v>604.509</v>
+        <v>630.7920000000001</v>
       </c>
       <c r="G25">
         <v>206.6</v>
@@ -3337,45 +3337,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M25">
-        <v>54.40581</v>
+        <v>92.60026560000003</v>
       </c>
       <c r="N25">
-        <v>29.19419000000001</v>
+        <v>-9.00026560000002</v>
       </c>
       <c r="O25">
-        <v>7.232924687295897</v>
+        <v>-2.229835568325758</v>
       </c>
       <c r="P25">
-        <v>21.96126531270411</v>
+        <v>-6.770430031674262</v>
       </c>
       <c r="Q25">
-        <v>112.6612653127041</v>
+        <v>83.92956996832574</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08546852949554939</v>
+        <v>0.08613120053495324</v>
       </c>
       <c r="T25">
-        <v>0.9161323209133808</v>
+        <v>0.9314365019619686</v>
       </c>
       <c r="U25">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.2477521961491617</v>
+        <v>0.2236719675031895</v>
       </c>
       <c r="W25">
-        <v>0.06770230234657544</v>
+        <v>0.1139649551705318</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.536600594679135</v>
+        <v>0.9028051859065076</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0928113016474921</v>
+        <v>0.09382130164749208</v>
       </c>
       <c r="C26">
-        <v>1232.898430938477</v>
+        <v>1171.762953437272</v>
       </c>
       <c r="D26">
-        <v>1657.090430938478</v>
+        <v>1622.237953437272</v>
       </c>
       <c r="E26">
-        <v>591.4920000000001</v>
+        <v>617.7750000000001</v>
       </c>
       <c r="F26">
-        <v>630.792</v>
+        <v>657.075</v>
       </c>
       <c r="G26">
         <v>206.6</v>
@@ -3419,37 +3419,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M26">
-        <v>92.60026560000001</v>
+        <v>96.45861000000002</v>
       </c>
       <c r="N26">
-        <v>-9.000265600000006</v>
+        <v>-12.85861000000001</v>
       </c>
       <c r="O26">
-        <v>-2.229835568325754</v>
+        <v>-3.185748866925576</v>
       </c>
       <c r="P26">
-        <v>-6.770430031674252</v>
+        <v>-9.672861133074438</v>
       </c>
       <c r="Q26">
-        <v>83.92956996832575</v>
+        <v>81.02713886692557</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08613120053495324</v>
+        <v>0.08666894987541927</v>
       </c>
       <c r="T26">
-        <v>0.9314365019619686</v>
+        <v>0.9438556553214613</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.2236719675031895</v>
+        <v>0.2147250888030619</v>
       </c>
       <c r="W26">
-        <v>0.1139649551705318</v>
+        <v>0.1152783569637105</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.9028051859065078</v>
+        <v>0.8666929784702474</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09382130164749208</v>
+        <v>0.09483130164749209</v>
       </c>
       <c r="C27">
-        <v>1171.762953437272</v>
+        <v>1112.06333429974</v>
       </c>
       <c r="D27">
-        <v>1622.237953437272</v>
+        <v>1588.82133429974</v>
       </c>
       <c r="E27">
-        <v>617.7750000000001</v>
+        <v>644.0580000000001</v>
       </c>
       <c r="F27">
-        <v>657.075</v>
+        <v>683.3580000000001</v>
       </c>
       <c r="G27">
         <v>206.6</v>
@@ -3501,37 +3501,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M27">
-        <v>96.45861000000002</v>
+        <v>100.3169544</v>
       </c>
       <c r="N27">
-        <v>-12.85861000000001</v>
+        <v>-16.71695440000001</v>
       </c>
       <c r="O27">
-        <v>-3.185748866925576</v>
+        <v>-4.141662165525394</v>
       </c>
       <c r="P27">
-        <v>-9.672861133074438</v>
+        <v>-12.57529223447461</v>
       </c>
       <c r="Q27">
-        <v>81.02713886692557</v>
+        <v>78.12470776552539</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08666894987541927</v>
+        <v>0.08722123298184387</v>
       </c>
       <c r="T27">
-        <v>0.9438556553214613</v>
+        <v>0.9566104614744542</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2147250888030619</v>
+        <v>0.2064664315414057</v>
       </c>
       <c r="W27">
-        <v>0.1152783569637105</v>
+        <v>0.1164907278497216</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8666929784702474</v>
+        <v>0.8333586331444687</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09483130164749209</v>
+        <v>0.09584130164749208</v>
       </c>
       <c r="C28">
-        <v>1112.06333429974</v>
+        <v>1053.712632325342</v>
       </c>
       <c r="D28">
-        <v>1588.82133429974</v>
+        <v>1556.753632325343</v>
       </c>
       <c r="E28">
-        <v>644.0580000000001</v>
+        <v>670.3410000000001</v>
       </c>
       <c r="F28">
-        <v>683.3580000000001</v>
+        <v>709.6410000000001</v>
       </c>
       <c r="G28">
         <v>206.6</v>
@@ -3583,37 +3583,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M28">
-        <v>100.3169544</v>
+        <v>104.1752988</v>
       </c>
       <c r="N28">
-        <v>-16.71695440000001</v>
+        <v>-20.57529880000001</v>
       </c>
       <c r="O28">
-        <v>-4.141662165525394</v>
+        <v>-5.097575464125215</v>
       </c>
       <c r="P28">
-        <v>-12.57529223447461</v>
+        <v>-15.4777233358748</v>
       </c>
       <c r="Q28">
-        <v>78.12470776552539</v>
+        <v>75.2222766641252</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08722123298184387</v>
+        <v>0.08778864713228007</v>
       </c>
       <c r="T28">
-        <v>0.9566104614744542</v>
+        <v>0.9697147143713645</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2064664315414057</v>
+        <v>0.1988195266695018</v>
       </c>
       <c r="W28">
-        <v>0.1164907278497216</v>
+        <v>0.1176132934849172</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8333586331444687</v>
+        <v>0.8024934985835624</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09584130164749208</v>
+        <v>0.112438896970061</v>
       </c>
       <c r="C29">
-        <v>1053.712632325342</v>
+        <v>639.6926201433465</v>
       </c>
       <c r="D29">
-        <v>1556.753632325343</v>
+        <v>1169.016620143347</v>
       </c>
       <c r="E29">
-        <v>670.3410000000001</v>
+        <v>696.6240000000001</v>
       </c>
       <c r="F29">
-        <v>709.6410000000001</v>
+        <v>735.9240000000001</v>
       </c>
       <c r="G29">
         <v>206.6</v>
@@ -3665,45 +3665,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M29">
-        <v>104.1752988</v>
+        <v>147.7735392</v>
       </c>
       <c r="N29">
-        <v>-20.57529880000001</v>
+        <v>-64.17353920000001</v>
       </c>
       <c r="O29">
-        <v>-5.097575464125215</v>
+        <v>-15.89913527146432</v>
       </c>
       <c r="P29">
-        <v>-15.4777233358748</v>
+        <v>-48.27440392853569</v>
       </c>
       <c r="Q29">
-        <v>75.2222766641252</v>
+        <v>42.42559607146431</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08778864713228007</v>
+        <v>0.08902126073490749</v>
       </c>
       <c r="T29">
-        <v>0.9697147143713645</v>
+        <v>0.9981815412218821</v>
       </c>
       <c r="U29">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1988195266695018</v>
+        <v>0.1401609767905587</v>
       </c>
       <c r="W29">
-        <v>0.1176132934849172</v>
+        <v>0.1726556758604558</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.8024934985835624</v>
+        <v>0.5657305120563831</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.112438896970061</v>
+        <v>0.113988896970061</v>
       </c>
       <c r="C30">
-        <v>639.6926201433465</v>
+        <v>586.8367345016013</v>
       </c>
       <c r="D30">
-        <v>1169.016620143347</v>
+        <v>1142.443734501602</v>
       </c>
       <c r="E30">
-        <v>696.6240000000001</v>
+        <v>722.9070000000002</v>
       </c>
       <c r="F30">
-        <v>735.9240000000001</v>
+        <v>762.2070000000001</v>
       </c>
       <c r="G30">
         <v>206.6</v>
@@ -3747,37 +3747,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M30">
-        <v>147.7735392</v>
+        <v>153.0511656</v>
       </c>
       <c r="N30">
-        <v>-64.17353920000001</v>
+        <v>-69.45116560000001</v>
       </c>
       <c r="O30">
-        <v>-15.89913527146432</v>
+        <v>-17.20667880251911</v>
       </c>
       <c r="P30">
-        <v>-48.27440392853569</v>
+        <v>-52.2444867974809</v>
       </c>
       <c r="Q30">
-        <v>42.42559607146431</v>
+        <v>38.45551320251911</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08902126073490749</v>
+        <v>0.08963001088610337</v>
       </c>
       <c r="T30">
-        <v>0.9981815412218821</v>
+        <v>1.012240436168669</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1401609767905587</v>
+        <v>0.1353278396598498</v>
       </c>
       <c r="W30">
-        <v>0.1726556758604558</v>
+        <v>0.1736261697963022</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5657305120563831</v>
+        <v>0.5462225633647837</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.113988896970061</v>
+        <v>0.115538896970061</v>
       </c>
       <c r="C31">
-        <v>586.8367345016014</v>
+        <v>535.1620540275369</v>
       </c>
       <c r="D31">
-        <v>1142.443734501602</v>
+        <v>1117.052054027537</v>
       </c>
       <c r="E31">
-        <v>722.907</v>
+        <v>749.1900000000001</v>
       </c>
       <c r="F31">
-        <v>762.207</v>
+        <v>788.49</v>
       </c>
       <c r="G31">
         <v>206.6</v>
@@ -3829,37 +3829,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M31">
-        <v>153.0511656</v>
+        <v>158.328792</v>
       </c>
       <c r="N31">
-        <v>-69.45116559999998</v>
+        <v>-74.72879199999998</v>
       </c>
       <c r="O31">
-        <v>-17.20667880251911</v>
+        <v>-18.5142223335739</v>
       </c>
       <c r="P31">
-        <v>-52.24448679748087</v>
+        <v>-56.21456966642608</v>
       </c>
       <c r="Q31">
-        <v>38.45551320251913</v>
+        <v>34.48543033357392</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08963001088610337</v>
+        <v>0.09025615389876199</v>
       </c>
       <c r="T31">
-        <v>1.012240436168669</v>
+        <v>1.026701013828222</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1353278396598498</v>
+        <v>0.1308169116711882</v>
       </c>
       <c r="W31">
-        <v>0.1736261697963022</v>
+        <v>0.1745319641364254</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5462225633647837</v>
+        <v>0.5280151445859576</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.115538896970061</v>
+        <v>0.117088896970061</v>
       </c>
       <c r="C32">
-        <v>535.1620540275369</v>
+        <v>484.5915316035356</v>
       </c>
       <c r="D32">
-        <v>1117.052054027537</v>
+        <v>1092.764531603536</v>
       </c>
       <c r="E32">
-        <v>749.1900000000001</v>
+        <v>775.4730000000001</v>
       </c>
       <c r="F32">
-        <v>788.49</v>
+        <v>814.773</v>
       </c>
       <c r="G32">
         <v>206.6</v>
@@ -3911,37 +3911,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M32">
-        <v>158.328792</v>
+        <v>163.6064184</v>
       </c>
       <c r="N32">
-        <v>-74.72879199999998</v>
+        <v>-80.00641840000002</v>
       </c>
       <c r="O32">
-        <v>-18.5142223335739</v>
+        <v>-19.82176586462871</v>
       </c>
       <c r="P32">
-        <v>-56.21456966642608</v>
+        <v>-60.18465253537131</v>
       </c>
       <c r="Q32">
-        <v>34.48543033357392</v>
+        <v>30.51534746462869</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09025615389876199</v>
+        <v>0.09090044598425129</v>
       </c>
       <c r="T32">
-        <v>1.026701013828222</v>
+        <v>1.041580738666312</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1308169116711882</v>
+        <v>0.1265970112946982</v>
       </c>
       <c r="W32">
-        <v>0.1745319641364254</v>
+        <v>0.1753793201320246</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5280151445859576</v>
+        <v>0.5109823979864105</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.117088896970061</v>
+        <v>0.1300275773306427</v>
       </c>
       <c r="C33">
-        <v>484.5915316035356</v>
+        <v>290.4427157758364</v>
       </c>
       <c r="D33">
-        <v>1092.764531603536</v>
+        <v>924.8987157758365</v>
       </c>
       <c r="E33">
-        <v>775.4730000000001</v>
+        <v>801.7560000000001</v>
       </c>
       <c r="F33">
-        <v>814.773</v>
+        <v>841.056</v>
       </c>
       <c r="G33">
         <v>206.6</v>
@@ -3993,45 +3993,45 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M33">
-        <v>163.6064184</v>
+        <v>198.3210048</v>
       </c>
       <c r="N33">
-        <v>-80.00641840000002</v>
+        <v>-114.7210048</v>
       </c>
       <c r="O33">
-        <v>-19.82176586462871</v>
+        <v>-28.42238088363853</v>
       </c>
       <c r="P33">
-        <v>-60.18465253537131</v>
+        <v>-86.29862391636149</v>
       </c>
       <c r="Q33">
-        <v>30.51534746462869</v>
+        <v>4.40137608363851</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09090044598425129</v>
+        <v>0.09184115895546341</v>
       </c>
       <c r="T33">
-        <v>1.041580738666312</v>
+        <v>1.063306211442573</v>
       </c>
       <c r="U33">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1265970112946982</v>
+        <v>0.1044371654881305</v>
       </c>
       <c r="W33">
-        <v>0.1753793201320246</v>
+        <v>0.2111737163778989</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.5109823979864105</v>
+        <v>0.4215388081777206</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1300275773306427</v>
+        <v>0.1319275773306428</v>
       </c>
       <c r="C34">
-        <v>290.4427157758364</v>
+        <v>243.7561747215256</v>
       </c>
       <c r="D34">
-        <v>924.8987157758365</v>
+        <v>904.4951747215256</v>
       </c>
       <c r="E34">
-        <v>801.7560000000001</v>
+        <v>828.0390000000001</v>
       </c>
       <c r="F34">
-        <v>841.056</v>
+        <v>867.3390000000001</v>
       </c>
       <c r="G34">
         <v>206.6</v>
@@ -4075,37 +4075,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M34">
-        <v>198.3210048</v>
+        <v>204.5185362</v>
       </c>
       <c r="N34">
-        <v>-114.7210048</v>
+        <v>-120.9185362</v>
       </c>
       <c r="O34">
-        <v>-28.42238088363853</v>
+        <v>-29.95783289869192</v>
       </c>
       <c r="P34">
-        <v>-86.29862391636149</v>
+        <v>-90.9607033013081</v>
       </c>
       <c r="Q34">
-        <v>4.40137608363851</v>
+        <v>-0.2607033013080979</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09184115895546341</v>
+        <v>0.09252834043241062</v>
       </c>
       <c r="T34">
-        <v>1.063306211442573</v>
+        <v>1.079176453404402</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1044371654881305</v>
+        <v>0.1012724028975811</v>
       </c>
       <c r="W34">
-        <v>0.2111737163778989</v>
+        <v>0.2119199673967504</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4215388081777206</v>
+        <v>0.4087649048996078</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1319275773306428</v>
+        <v>0.1338275773306427</v>
       </c>
       <c r="C35">
-        <v>243.7561747215256</v>
+        <v>197.9504196476717</v>
       </c>
       <c r="D35">
-        <v>904.4951747215256</v>
+        <v>884.9724196476718</v>
       </c>
       <c r="E35">
-        <v>828.0390000000001</v>
+        <v>854.3220000000001</v>
       </c>
       <c r="F35">
-        <v>867.3390000000001</v>
+        <v>893.6220000000001</v>
       </c>
       <c r="G35">
         <v>206.6</v>
@@ -4157,37 +4157,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M35">
-        <v>204.5185362</v>
+        <v>210.7160676</v>
       </c>
       <c r="N35">
-        <v>-120.9185362</v>
+        <v>-127.1160676</v>
       </c>
       <c r="O35">
-        <v>-29.95783289869192</v>
+        <v>-31.49328491374531</v>
       </c>
       <c r="P35">
-        <v>-90.9607033013081</v>
+        <v>-95.62278268625471</v>
       </c>
       <c r="Q35">
-        <v>-0.2607033013080979</v>
+        <v>-4.922782686254706</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09252834043241062</v>
+        <v>0.09323634559047744</v>
       </c>
       <c r="T35">
-        <v>1.079176453404402</v>
+        <v>1.095527611789318</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.1012724028975811</v>
+        <v>0.0982938028123581</v>
       </c>
       <c r="W35">
-        <v>0.2119199673967504</v>
+        <v>0.212622321296846</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4087649048996078</v>
+        <v>0.3967424076966781</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1338275773306427</v>
+        <v>0.1357275773306428</v>
       </c>
       <c r="C36">
-        <v>197.9504196476717</v>
+        <v>152.9696225175619</v>
       </c>
       <c r="D36">
-        <v>884.9724196476718</v>
+        <v>866.2746225175622</v>
       </c>
       <c r="E36">
-        <v>854.3220000000001</v>
+        <v>880.6050000000002</v>
       </c>
       <c r="F36">
-        <v>893.6220000000001</v>
+        <v>919.9050000000002</v>
       </c>
       <c r="G36">
         <v>206.6</v>
@@ -4239,37 +4239,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M36">
-        <v>210.7160676</v>
+        <v>216.9135990000001</v>
       </c>
       <c r="N36">
-        <v>-127.1160676</v>
+        <v>-133.3135990000001</v>
       </c>
       <c r="O36">
-        <v>-31.49328491374531</v>
+        <v>-33.02873692879871</v>
       </c>
       <c r="P36">
-        <v>-95.62278268625471</v>
+        <v>-100.2848620712014</v>
       </c>
       <c r="Q36">
-        <v>-4.922782686254706</v>
+        <v>-9.584862071201357</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09323634559047744</v>
+        <v>0.09396613552263863</v>
       </c>
       <c r="T36">
-        <v>1.095527611789318</v>
+        <v>1.112381882739922</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0982938028123581</v>
+        <v>0.09548540844629071</v>
       </c>
       <c r="W36">
-        <v>0.212622321296846</v>
+        <v>0.2132845406883647</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3967424076966781</v>
+        <v>0.3854069103339158</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1357275773306428</v>
+        <v>0.1376275773306427</v>
       </c>
       <c r="C37">
-        <v>152.9696225175619</v>
+        <v>108.7625758354101</v>
       </c>
       <c r="D37">
-        <v>866.2746225175622</v>
+        <v>848.3505758354103</v>
       </c>
       <c r="E37">
-        <v>880.6050000000002</v>
+        <v>906.8880000000003</v>
       </c>
       <c r="F37">
-        <v>919.9050000000002</v>
+        <v>946.1880000000002</v>
       </c>
       <c r="G37">
         <v>206.6</v>
@@ -4321,37 +4321,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M37">
-        <v>216.9135990000001</v>
+        <v>223.1111304000001</v>
       </c>
       <c r="N37">
-        <v>-133.3135990000001</v>
+        <v>-139.5111304000001</v>
       </c>
       <c r="O37">
-        <v>-33.02873692879871</v>
+        <v>-34.56418894385209</v>
       </c>
       <c r="P37">
-        <v>-100.2848620712014</v>
+        <v>-104.946941456148</v>
       </c>
       <c r="Q37">
-        <v>-9.584862071201357</v>
+        <v>-14.24694145614798</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09396613552263863</v>
+        <v>0.09471873139017986</v>
       </c>
       <c r="T37">
-        <v>1.112381882739922</v>
+        <v>1.129762849657734</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.09548540844629071</v>
+        <v>0.09283303598944931</v>
       </c>
       <c r="W37">
-        <v>0.2132845406883647</v>
+        <v>0.2139099701136878</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3854069103339158</v>
+        <v>0.3747011628246404</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1376275773306427</v>
+        <v>0.1395275773306427</v>
       </c>
       <c r="C38">
-        <v>108.7625758354103</v>
+        <v>65.28222431952599</v>
       </c>
       <c r="D38">
-        <v>848.3505758354103</v>
+        <v>831.153224319526</v>
       </c>
       <c r="E38">
-        <v>906.888</v>
+        <v>933.171</v>
       </c>
       <c r="F38">
-        <v>946.188</v>
+        <v>972.471</v>
       </c>
       <c r="G38">
         <v>206.6</v>
@@ -4403,37 +4403,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M38">
-        <v>223.1111304</v>
+        <v>229.3086618</v>
       </c>
       <c r="N38">
-        <v>-139.5111304</v>
+        <v>-145.7086618</v>
       </c>
       <c r="O38">
-        <v>-34.56418894385208</v>
+        <v>-36.09964095890547</v>
       </c>
       <c r="P38">
-        <v>-104.9469414561479</v>
+        <v>-109.6090208410945</v>
       </c>
       <c r="Q38">
-        <v>-14.24694145614792</v>
+        <v>-18.90902084109455</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09471873139017986</v>
+        <v>0.09549521919002399</v>
       </c>
       <c r="T38">
-        <v>1.129762849657734</v>
+        <v>1.147695593303095</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.09283303598944934</v>
+        <v>0.09032403501676149</v>
       </c>
       <c r="W38">
-        <v>0.2139099701136878</v>
+        <v>0.2145015925430477</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3747011628246405</v>
+        <v>0.3645741043699204</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1395275773306427</v>
+        <v>0.1414275773306428</v>
       </c>
       <c r="C39">
-        <v>65.28222431952599</v>
+        <v>22.48525240589174</v>
       </c>
       <c r="D39">
-        <v>831.153224319526</v>
+        <v>814.6392524058919</v>
       </c>
       <c r="E39">
-        <v>933.171</v>
+        <v>959.4540000000002</v>
       </c>
       <c r="F39">
-        <v>972.471</v>
+        <v>998.7540000000001</v>
       </c>
       <c r="G39">
         <v>206.6</v>
@@ -4485,37 +4485,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M39">
-        <v>229.3086618</v>
+        <v>235.5061932</v>
       </c>
       <c r="N39">
-        <v>-145.7086618</v>
+        <v>-151.9061932</v>
       </c>
       <c r="O39">
-        <v>-36.09964095890547</v>
+        <v>-37.63509297395886</v>
       </c>
       <c r="P39">
-        <v>-109.6090208410945</v>
+        <v>-114.2711002260412</v>
       </c>
       <c r="Q39">
-        <v>-18.90902084109455</v>
+        <v>-23.57110022604115</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09549521919002399</v>
+        <v>0.09629675498341148</v>
       </c>
       <c r="T39">
-        <v>1.147695593303095</v>
+        <v>1.166206812549919</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09032403501676149</v>
+        <v>0.08794708672684672</v>
       </c>
       <c r="W39">
-        <v>0.2145015925430477</v>
+        <v>0.2150620769498096</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3645741043699204</v>
+        <v>0.3549800489917647</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1414275773306428</v>
+        <v>0.1433275773306427</v>
       </c>
       <c r="C40">
-        <v>22.48525240589174</v>
+        <v>-19.66828003155092</v>
       </c>
       <c r="D40">
-        <v>814.6392524058919</v>
+        <v>798.7687199684491</v>
       </c>
       <c r="E40">
-        <v>959.4540000000002</v>
+        <v>985.7370000000001</v>
       </c>
       <c r="F40">
-        <v>998.7540000000001</v>
+        <v>1025.037</v>
       </c>
       <c r="G40">
         <v>206.6</v>
@@ -4567,37 +4567,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M40">
-        <v>235.5061932</v>
+        <v>241.7037246</v>
       </c>
       <c r="N40">
-        <v>-151.9061932</v>
+        <v>-158.1037246</v>
       </c>
       <c r="O40">
-        <v>-37.63509297395886</v>
+        <v>-39.17054498901225</v>
       </c>
       <c r="P40">
-        <v>-114.2711002260412</v>
+        <v>-118.9331796109878</v>
       </c>
       <c r="Q40">
-        <v>-23.57110022604115</v>
+        <v>-28.23317961098776</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09629675498341148</v>
+        <v>0.09712457063887724</v>
       </c>
       <c r="T40">
-        <v>1.166206812549919</v>
+        <v>1.18532495701795</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08794708672684672</v>
+        <v>0.08569203322103014</v>
       </c>
       <c r="W40">
-        <v>0.2150620769498096</v>
+        <v>0.2155938185664811</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3549800489917647</v>
+        <v>0.3458779964535142</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1433275773306427</v>
+        <v>0.1452275773306428</v>
       </c>
       <c r="C41">
-        <v>-19.66828003155092</v>
+        <v>-61.21526019364592</v>
       </c>
       <c r="D41">
-        <v>798.7687199684491</v>
+        <v>783.5047398063542</v>
       </c>
       <c r="E41">
-        <v>985.7370000000001</v>
+        <v>1012.02</v>
       </c>
       <c r="F41">
-        <v>1025.037</v>
+        <v>1051.32</v>
       </c>
       <c r="G41">
         <v>206.6</v>
@@ -4649,37 +4649,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M41">
-        <v>241.7037246</v>
+        <v>247.901256</v>
       </c>
       <c r="N41">
-        <v>-158.1037246</v>
+        <v>-164.301256</v>
       </c>
       <c r="O41">
-        <v>-39.17054498901225</v>
+        <v>-40.70599700406564</v>
       </c>
       <c r="P41">
-        <v>-118.9331796109878</v>
+        <v>-123.5952589959344</v>
       </c>
       <c r="Q41">
-        <v>-28.23317961098776</v>
+        <v>-32.89525899593438</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09712457063887724</v>
+        <v>0.09797998014952519</v>
       </c>
       <c r="T41">
-        <v>1.18532495701795</v>
+        <v>1.205080372968249</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08569203322103014</v>
+        <v>0.08354973239050438</v>
       </c>
       <c r="W41">
-        <v>0.2155938185664811</v>
+        <v>0.2160989731023191</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3458779964535142</v>
+        <v>0.3372310465421765</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1452275773306428</v>
+        <v>0.1471275773306427</v>
       </c>
       <c r="C42">
-        <v>-61.21526019364592</v>
+        <v>-102.1898085840153</v>
       </c>
       <c r="D42">
-        <v>783.5047398063542</v>
+        <v>768.8131914159848</v>
       </c>
       <c r="E42">
-        <v>1012.02</v>
+        <v>1038.303</v>
       </c>
       <c r="F42">
-        <v>1051.32</v>
+        <v>1077.603</v>
       </c>
       <c r="G42">
         <v>206.6</v>
@@ -4731,37 +4731,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M42">
-        <v>247.901256</v>
+        <v>254.0987874</v>
       </c>
       <c r="N42">
-        <v>-164.301256</v>
+        <v>-170.4987874</v>
       </c>
       <c r="O42">
-        <v>-40.70599700406564</v>
+        <v>-42.24144901911903</v>
       </c>
       <c r="P42">
-        <v>-123.5952589959344</v>
+        <v>-128.257338380881</v>
       </c>
       <c r="Q42">
-        <v>-32.89525899593438</v>
+        <v>-37.55733838088098</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09797998014952519</v>
+        <v>0.09886438659273747</v>
       </c>
       <c r="T42">
-        <v>1.205080372968249</v>
+        <v>1.225505464035508</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08354973239050438</v>
+        <v>0.08151193403951648</v>
       </c>
       <c r="W42">
-        <v>0.2160989731023191</v>
+        <v>0.216579485953482</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3372310465421765</v>
+        <v>0.329005899065538</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1471275773306427</v>
+        <v>0.1490275773306428</v>
       </c>
       <c r="C43">
-        <v>-102.1898085840153</v>
+        <v>-142.6235336273006</v>
       </c>
       <c r="D43">
-        <v>768.8131914159848</v>
+        <v>754.6624663726996</v>
       </c>
       <c r="E43">
-        <v>1038.303</v>
+        <v>1064.586</v>
       </c>
       <c r="F43">
-        <v>1077.603</v>
+        <v>1103.886</v>
       </c>
       <c r="G43">
         <v>206.6</v>
@@ -4813,37 +4813,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M43">
-        <v>254.0987874</v>
+        <v>260.2963188000001</v>
       </c>
       <c r="N43">
-        <v>-170.4987874</v>
+        <v>-176.6963188</v>
       </c>
       <c r="O43">
-        <v>-42.24144901911903</v>
+        <v>-43.77690103417242</v>
       </c>
       <c r="P43">
-        <v>-128.257338380881</v>
+        <v>-132.9194177658276</v>
       </c>
       <c r="Q43">
-        <v>-37.55733838088098</v>
+        <v>-42.2194177658276</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09886438659273747</v>
+        <v>0.09977928980985365</v>
       </c>
       <c r="T43">
-        <v>1.225505464035508</v>
+        <v>1.246634868587844</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08151193403951648</v>
+        <v>0.07957117370524228</v>
       </c>
       <c r="W43">
-        <v>0.216579485953482</v>
+        <v>0.2170371172403039</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.329005899065538</v>
+        <v>0.3211724252782633</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1490275773306428</v>
+        <v>0.1509275773306427</v>
       </c>
       <c r="C44">
-        <v>-142.6235336273004</v>
+        <v>-182.5457586766747</v>
       </c>
       <c r="D44">
-        <v>754.6624663726996</v>
+        <v>741.0232413233254</v>
       </c>
       <c r="E44">
-        <v>1064.586</v>
+        <v>1090.869</v>
       </c>
       <c r="F44">
-        <v>1103.886</v>
+        <v>1130.169</v>
       </c>
       <c r="G44">
         <v>206.6</v>
@@ -4895,37 +4895,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M44">
-        <v>260.2963188</v>
+        <v>266.4938502000001</v>
       </c>
       <c r="N44">
-        <v>-176.6963188</v>
+        <v>-182.8938502</v>
       </c>
       <c r="O44">
-        <v>-43.7769010341724</v>
+        <v>-45.31235304922581</v>
       </c>
       <c r="P44">
-        <v>-132.9194177658276</v>
+        <v>-137.5814971507742</v>
       </c>
       <c r="Q44">
-        <v>-42.21941776582757</v>
+        <v>-46.88149715077422</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09977928980985365</v>
+        <v>0.100726294894237</v>
       </c>
       <c r="T44">
-        <v>1.246634868587844</v>
+        <v>1.268505655756052</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07957117370524229</v>
+        <v>0.07772068129349244</v>
       </c>
       <c r="W44">
-        <v>0.2170371172403039</v>
+        <v>0.2174734633509945</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3211724252782634</v>
+        <v>0.3137032991090014</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1509275773306427</v>
+        <v>0.1528275773306428</v>
       </c>
       <c r="C45">
-        <v>-182.5457586766747</v>
+        <v>-221.9837248417473</v>
       </c>
       <c r="D45">
-        <v>741.0232413233254</v>
+        <v>727.8682751582527</v>
       </c>
       <c r="E45">
-        <v>1090.869</v>
+        <v>1117.152</v>
       </c>
       <c r="F45">
-        <v>1130.169</v>
+        <v>1156.452</v>
       </c>
       <c r="G45">
         <v>206.6</v>
@@ -4977,37 +4977,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M45">
-        <v>266.4938502000001</v>
+        <v>272.6913816</v>
       </c>
       <c r="N45">
-        <v>-182.8938502</v>
+        <v>-189.0913816</v>
       </c>
       <c r="O45">
-        <v>-45.31235304922581</v>
+        <v>-46.84780506427919</v>
       </c>
       <c r="P45">
-        <v>-137.5814971507742</v>
+        <v>-142.2435765357208</v>
       </c>
       <c r="Q45">
-        <v>-46.88149715077422</v>
+        <v>-51.54357653572079</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.100726294894237</v>
+        <v>0.101707121588777</v>
       </c>
       <c r="T45">
-        <v>1.268505655756052</v>
+        <v>1.291157542465981</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07772068129349244</v>
+        <v>0.07595430217318581</v>
       </c>
       <c r="W45">
-        <v>0.2174734633509945</v>
+        <v>0.2178899755475628</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3137032991090014</v>
+        <v>0.306573678674706</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1528275773306428</v>
+        <v>0.1547275773306427</v>
       </c>
       <c r="C46">
-        <v>-221.9837248417473</v>
+        <v>-260.962772589168</v>
       </c>
       <c r="D46">
-        <v>727.8682751582527</v>
+        <v>715.1722274108321</v>
       </c>
       <c r="E46">
-        <v>1117.152</v>
+        <v>1143.435</v>
       </c>
       <c r="F46">
-        <v>1156.452</v>
+        <v>1182.735</v>
       </c>
       <c r="G46">
         <v>206.6</v>
@@ -5059,37 +5059,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M46">
-        <v>272.6913816</v>
+        <v>278.8889130000001</v>
       </c>
       <c r="N46">
-        <v>-189.0913816</v>
+        <v>-195.288913</v>
       </c>
       <c r="O46">
-        <v>-46.84780506427919</v>
+        <v>-48.38325707933259</v>
       </c>
       <c r="P46">
-        <v>-142.2435765357208</v>
+        <v>-146.9056559206674</v>
       </c>
       <c r="Q46">
-        <v>-51.54357653572079</v>
+        <v>-56.20565592066744</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.101707121588777</v>
+        <v>0.1027236147085729</v>
       </c>
       <c r="T46">
-        <v>1.291157542465981</v>
+        <v>1.314633134147181</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07595430217318581</v>
+        <v>0.07426642879155944</v>
       </c>
       <c r="W46">
-        <v>0.2178899755475628</v>
+        <v>0.2182879760909503</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.306573678674706</v>
+        <v>0.2997609302597124</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1547275773306427</v>
+        <v>0.1566275773306428</v>
       </c>
       <c r="C47">
-        <v>-260.962772589168</v>
+        <v>-299.5065046633398</v>
       </c>
       <c r="D47">
-        <v>715.1722274108321</v>
+        <v>702.9114953366602</v>
       </c>
       <c r="E47">
-        <v>1143.435</v>
+        <v>1169.718</v>
       </c>
       <c r="F47">
-        <v>1182.735</v>
+        <v>1209.018</v>
       </c>
       <c r="G47">
         <v>206.6</v>
@@ -5141,37 +5141,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M47">
-        <v>278.8889130000001</v>
+        <v>285.0864444</v>
       </c>
       <c r="N47">
-        <v>-195.288913</v>
+        <v>-201.4864444</v>
       </c>
       <c r="O47">
-        <v>-48.38325707933259</v>
+        <v>-49.91870909438596</v>
       </c>
       <c r="P47">
-        <v>-146.9056559206674</v>
+        <v>-151.567735305614</v>
       </c>
       <c r="Q47">
-        <v>-56.20565592066744</v>
+        <v>-60.867735305614</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1027236147085729</v>
+        <v>0.1037777557216946</v>
       </c>
       <c r="T47">
-        <v>1.314633134147181</v>
+        <v>1.338978192186943</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07426642879155944</v>
+        <v>0.07265194120913426</v>
       </c>
       <c r="W47">
-        <v>0.2182879760909503</v>
+        <v>0.2186686722628862</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2997609302597124</v>
+        <v>0.2932443882975448</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1566275773306428</v>
+        <v>0.1585275773306427</v>
       </c>
       <c r="C48">
-        <v>-299.5065046633398</v>
+        <v>-337.6369325311666</v>
       </c>
       <c r="D48">
-        <v>702.9114953366602</v>
+        <v>691.0640674688335</v>
       </c>
       <c r="E48">
-        <v>1169.718</v>
+        <v>1196.001</v>
       </c>
       <c r="F48">
-        <v>1209.018</v>
+        <v>1235.301</v>
       </c>
       <c r="G48">
         <v>206.6</v>
@@ -5223,37 +5223,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M48">
-        <v>285.0864444</v>
+        <v>291.2839758000001</v>
       </c>
       <c r="N48">
-        <v>-201.4864444</v>
+        <v>-207.6839758</v>
       </c>
       <c r="O48">
-        <v>-49.91870909438596</v>
+        <v>-51.45416110943937</v>
       </c>
       <c r="P48">
-        <v>-151.567735305614</v>
+        <v>-156.2298146905607</v>
       </c>
       <c r="Q48">
-        <v>-60.867735305614</v>
+        <v>-65.52981469056066</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1037777557216946</v>
+        <v>0.1048716756409719</v>
       </c>
       <c r="T48">
-        <v>1.338978192186943</v>
+        <v>1.364241931662169</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07265194120913426</v>
+        <v>0.07110615522596117</v>
       </c>
       <c r="W48">
-        <v>0.2186686722628862</v>
+        <v>0.2190331685977183</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2932443882975448</v>
+        <v>0.2870051459933417</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1585275773306427</v>
+        <v>0.1604275773306427</v>
       </c>
       <c r="C49">
-        <v>-337.6369325311666</v>
+        <v>-375.3746082624995</v>
       </c>
       <c r="D49">
-        <v>691.0640674688335</v>
+        <v>679.6093917375008</v>
       </c>
       <c r="E49">
-        <v>1196.001</v>
+        <v>1222.284</v>
       </c>
       <c r="F49">
-        <v>1235.301</v>
+        <v>1261.584</v>
       </c>
       <c r="G49">
         <v>206.6</v>
@@ -5305,37 +5305,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M49">
-        <v>291.2839758000001</v>
+        <v>297.4815072000001</v>
       </c>
       <c r="N49">
-        <v>-207.6839758</v>
+        <v>-213.8815072</v>
       </c>
       <c r="O49">
-        <v>-51.45416110943937</v>
+        <v>-52.98961312449276</v>
       </c>
       <c r="P49">
-        <v>-156.2298146905607</v>
+        <v>-160.8918940755073</v>
       </c>
       <c r="Q49">
-        <v>-65.52981469056066</v>
+        <v>-70.19189407550728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1048716756409719</v>
+        <v>0.1060076694032983</v>
       </c>
       <c r="T49">
-        <v>1.364241931662169</v>
+        <v>1.390477353424903</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07110615522596117</v>
+        <v>0.06962477699208698</v>
       </c>
       <c r="W49">
-        <v>0.2190331685977183</v>
+        <v>0.2193824775852659</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2870051459933417</v>
+        <v>0.2810258721184804</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1604275773306427</v>
+        <v>0.1623275773306427</v>
       </c>
       <c r="C50">
-        <v>-375.3746082624992</v>
+        <v>-412.7387435085993</v>
       </c>
       <c r="D50">
-        <v>679.6093917375008</v>
+        <v>668.5282564914006</v>
       </c>
       <c r="E50">
-        <v>1222.284</v>
+        <v>1248.567</v>
       </c>
       <c r="F50">
-        <v>1261.584</v>
+        <v>1287.867</v>
       </c>
       <c r="G50">
         <v>206.6</v>
@@ -5387,37 +5387,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M50">
-        <v>297.4815072</v>
+        <v>303.6790386</v>
       </c>
       <c r="N50">
-        <v>-213.8815072</v>
+        <v>-220.0790386</v>
       </c>
       <c r="O50">
-        <v>-52.98961312449274</v>
+        <v>-54.52506513954613</v>
       </c>
       <c r="P50">
-        <v>-160.8918940755073</v>
+        <v>-165.5539734604538</v>
       </c>
       <c r="Q50">
-        <v>-70.19189407550725</v>
+        <v>-74.85397346045384</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1060076694032983</v>
+        <v>0.1071882119406179</v>
       </c>
       <c r="T50">
-        <v>1.390477353424903</v>
+        <v>1.417741615256764</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.069624776992087</v>
+        <v>0.06820386317592195</v>
       </c>
       <c r="W50">
-        <v>0.2193824775852659</v>
+        <v>0.2197175290631176</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2810258721184804</v>
+        <v>0.2752906502385114</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1623275773306427</v>
+        <v>0.1642275773306427</v>
       </c>
       <c r="C51">
-        <v>-412.7387435085993</v>
+        <v>-449.7473170275726</v>
       </c>
       <c r="D51">
-        <v>668.5282564914006</v>
+        <v>657.8026829724274</v>
       </c>
       <c r="E51">
-        <v>1248.567</v>
+        <v>1274.85</v>
       </c>
       <c r="F51">
-        <v>1287.867</v>
+        <v>1314.15</v>
       </c>
       <c r="G51">
         <v>206.6</v>
@@ -5469,37 +5469,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M51">
-        <v>303.6790386</v>
+        <v>309.87657</v>
       </c>
       <c r="N51">
-        <v>-220.0790386</v>
+        <v>-226.27657</v>
       </c>
       <c r="O51">
-        <v>-54.52506513954613</v>
+        <v>-56.06051715459952</v>
       </c>
       <c r="P51">
-        <v>-165.5539734604538</v>
+        <v>-170.2160528454005</v>
       </c>
       <c r="Q51">
-        <v>-74.85397346045384</v>
+        <v>-79.51605284540047</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1071882119406179</v>
+        <v>0.1084159761794302</v>
       </c>
       <c r="T51">
-        <v>1.417741615256764</v>
+        <v>1.446096447561899</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06820386317592195</v>
+        <v>0.06683978591240351</v>
       </c>
       <c r="W51">
-        <v>0.2197175290631176</v>
+        <v>0.2200391784818553</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2752906502385114</v>
+        <v>0.2697848372337412</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1642275773306427</v>
+        <v>0.1661275773306428</v>
       </c>
       <c r="C52">
-        <v>-449.7473170275726</v>
+        <v>-486.4171720226939</v>
       </c>
       <c r="D52">
-        <v>657.8026829724274</v>
+        <v>647.4158279773063</v>
       </c>
       <c r="E52">
-        <v>1274.85</v>
+        <v>1301.133</v>
       </c>
       <c r="F52">
-        <v>1314.15</v>
+        <v>1340.433</v>
       </c>
       <c r="G52">
         <v>206.6</v>
@@ -5551,37 +5551,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M52">
-        <v>309.87657</v>
+        <v>316.0741014000001</v>
       </c>
       <c r="N52">
-        <v>-226.27657</v>
+        <v>-232.4741014000001</v>
       </c>
       <c r="O52">
-        <v>-56.06051715459952</v>
+        <v>-57.59596916965292</v>
       </c>
       <c r="P52">
-        <v>-170.2160528454005</v>
+        <v>-174.8781322303471</v>
       </c>
       <c r="Q52">
-        <v>-79.51605284540047</v>
+        <v>-84.17813223034712</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1084159761794302</v>
+        <v>0.1096938532443166</v>
       </c>
       <c r="T52">
-        <v>1.446096447561899</v>
+        <v>1.475608619961122</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06683978591240351</v>
+        <v>0.06552920187490539</v>
       </c>
       <c r="W52">
-        <v>0.2200391784818553</v>
+        <v>0.2203482141978973</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2697848372337412</v>
+        <v>0.2644949384644522</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1661275773306428</v>
+        <v>0.1680275773306427</v>
       </c>
       <c r="C53">
-        <v>-486.4171720226939</v>
+        <v>-522.7641044021218</v>
       </c>
       <c r="D53">
-        <v>647.4158279773063</v>
+        <v>637.3518955978783</v>
       </c>
       <c r="E53">
-        <v>1301.133</v>
+        <v>1327.416</v>
       </c>
       <c r="F53">
-        <v>1340.433</v>
+        <v>1366.716</v>
       </c>
       <c r="G53">
         <v>206.6</v>
@@ -5633,37 +5633,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M53">
-        <v>316.0741014000001</v>
+        <v>322.2716328</v>
       </c>
       <c r="N53">
-        <v>-232.4741014000001</v>
+        <v>-238.6716328</v>
       </c>
       <c r="O53">
-        <v>-57.59596916965292</v>
+        <v>-59.1314211847063</v>
       </c>
       <c r="P53">
-        <v>-174.8781322303471</v>
+        <v>-179.5402116152937</v>
       </c>
       <c r="Q53">
-        <v>-84.17813223034712</v>
+        <v>-88.84021161529368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1096938532443166</v>
+        <v>0.1110249751869065</v>
       </c>
       <c r="T53">
-        <v>1.475608619961122</v>
+        <v>1.506350466210311</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06552920187490539</v>
+        <v>0.06426902491577262</v>
       </c>
       <c r="W53">
-        <v>0.2203482141978973</v>
+        <v>0.2206453639248608</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2644949384644522</v>
+        <v>0.2594084973401358</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1680275773306427</v>
+        <v>0.1699275773306427</v>
       </c>
       <c r="C54">
-        <v>-522.7641044021218</v>
+        <v>-558.8029429327512</v>
       </c>
       <c r="D54">
-        <v>637.3518955978783</v>
+        <v>627.596057067249</v>
       </c>
       <c r="E54">
-        <v>1327.416</v>
+        <v>1353.699</v>
       </c>
       <c r="F54">
-        <v>1366.716</v>
+        <v>1392.999</v>
       </c>
       <c r="G54">
         <v>206.6</v>
@@ -5715,37 +5715,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M54">
-        <v>322.2716328</v>
+        <v>328.4691642000001</v>
       </c>
       <c r="N54">
-        <v>-238.6716328</v>
+        <v>-244.8691642000001</v>
       </c>
       <c r="O54">
-        <v>-59.1314211847063</v>
+        <v>-60.6668731997597</v>
       </c>
       <c r="P54">
-        <v>-179.5402116152937</v>
+        <v>-184.2022910002404</v>
       </c>
       <c r="Q54">
-        <v>-88.84021161529368</v>
+        <v>-93.50229100024036</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1110249751869065</v>
+        <v>0.1124127406164151</v>
       </c>
       <c r="T54">
-        <v>1.506350466210311</v>
+        <v>1.53840047612968</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06426902491577262</v>
+        <v>0.06305640180415424</v>
       </c>
       <c r="W54">
-        <v>0.2206453639248608</v>
+        <v>0.2209313004545804</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2594084973401358</v>
+        <v>0.2545139973903219</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1699275773306427</v>
+        <v>0.1718275773306427</v>
       </c>
       <c r="C55">
-        <v>-558.8029429327512</v>
+        <v>-594.5476221436378</v>
       </c>
       <c r="D55">
-        <v>627.596057067249</v>
+        <v>618.1343778563623</v>
       </c>
       <c r="E55">
-        <v>1353.699</v>
+        <v>1379.982</v>
       </c>
       <c r="F55">
-        <v>1392.999</v>
+        <v>1419.282</v>
       </c>
       <c r="G55">
         <v>206.6</v>
@@ -5797,37 +5797,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M55">
-        <v>328.4691642000001</v>
+        <v>334.6666956</v>
       </c>
       <c r="N55">
-        <v>-244.8691642000001</v>
+        <v>-251.0666956</v>
       </c>
       <c r="O55">
-        <v>-60.6668731997597</v>
+        <v>-62.20232521481308</v>
       </c>
       <c r="P55">
-        <v>-184.2022910002404</v>
+        <v>-188.8643703851869</v>
       </c>
       <c r="Q55">
-        <v>-93.50229100024036</v>
+        <v>-98.16437038518693</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1124127406164151</v>
+        <v>0.1138608436732937</v>
       </c>
       <c r="T55">
-        <v>1.53840047612968</v>
+        <v>1.571843964741195</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06305640180415424</v>
+        <v>0.06188869065963288</v>
       </c>
       <c r="W55">
-        <v>0.2209313004545804</v>
+        <v>0.2212066467424586</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2545139973903219</v>
+        <v>0.2498007752164271</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1718275773306427</v>
+        <v>0.1737275773306428</v>
       </c>
       <c r="C56">
-        <v>-594.5476221436378</v>
+        <v>-630.0112487327867</v>
       </c>
       <c r="D56">
-        <v>618.1343778563623</v>
+        <v>608.9537512672135</v>
       </c>
       <c r="E56">
-        <v>1379.982</v>
+        <v>1406.265</v>
       </c>
       <c r="F56">
-        <v>1419.282</v>
+        <v>1445.565</v>
       </c>
       <c r="G56">
         <v>206.6</v>
@@ -5879,37 +5879,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M56">
-        <v>334.6666956</v>
+        <v>340.8642270000001</v>
       </c>
       <c r="N56">
-        <v>-251.0666956</v>
+        <v>-257.2642270000001</v>
       </c>
       <c r="O56">
-        <v>-62.20232521481308</v>
+        <v>-63.73777722986648</v>
       </c>
       <c r="P56">
-        <v>-188.8643703851869</v>
+        <v>-193.5264497701336</v>
       </c>
       <c r="Q56">
-        <v>-98.16437038518693</v>
+        <v>-102.8264497701336</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1138608436732937</v>
+        <v>0.1153733068660336</v>
       </c>
       <c r="T56">
-        <v>1.571843964741195</v>
+        <v>1.606773830624332</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06188869065963288</v>
+        <v>0.06076344173854863</v>
       </c>
       <c r="W56">
-        <v>0.2212066467424586</v>
+        <v>0.2214719804380502</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2498007752164271</v>
+        <v>0.2452589429397647</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1737275773306428</v>
+        <v>0.1756275773306427</v>
       </c>
       <c r="C57">
-        <v>-630.0112487327867</v>
+        <v>-665.2061621428401</v>
       </c>
       <c r="D57">
-        <v>608.9537512672135</v>
+        <v>600.0418378571601</v>
       </c>
       <c r="E57">
-        <v>1406.265</v>
+        <v>1432.548</v>
       </c>
       <c r="F57">
-        <v>1445.565</v>
+        <v>1471.848</v>
       </c>
       <c r="G57">
         <v>206.6</v>
@@ -5961,37 +5961,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M57">
-        <v>340.8642270000001</v>
+        <v>347.0617584</v>
       </c>
       <c r="N57">
-        <v>-257.2642270000001</v>
+        <v>-263.4617584</v>
       </c>
       <c r="O57">
-        <v>-63.73777722986648</v>
+        <v>-65.27322924491986</v>
       </c>
       <c r="P57">
-        <v>-193.5264497701336</v>
+        <v>-198.1885291550801</v>
       </c>
       <c r="Q57">
-        <v>-102.8264497701336</v>
+        <v>-107.4885291550801</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1153733068660336</v>
+        <v>0.1169545183857162</v>
       </c>
       <c r="T57">
-        <v>1.606773830624332</v>
+        <v>1.643291417683976</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06076344173854863</v>
+        <v>0.0596783802789317</v>
       </c>
       <c r="W57">
-        <v>0.2214719804380502</v>
+        <v>0.2217278379302279</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2452589429397647</v>
+        <v>0.2408793189586975</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1756275773306427</v>
+        <v>0.1775275773306428</v>
       </c>
       <c r="C58">
-        <v>-665.2061621428401</v>
+        <v>-700.1439898944124</v>
       </c>
       <c r="D58">
-        <v>600.0418378571601</v>
+        <v>591.3870101055879</v>
       </c>
       <c r="E58">
-        <v>1432.548</v>
+        <v>1458.831</v>
       </c>
       <c r="F58">
-        <v>1471.848</v>
+        <v>1498.131</v>
       </c>
       <c r="G58">
         <v>206.6</v>
@@ -6043,37 +6043,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M58">
-        <v>347.0617584</v>
+        <v>353.2592898000001</v>
       </c>
       <c r="N58">
-        <v>-263.4617584</v>
+        <v>-269.6592898000001</v>
       </c>
       <c r="O58">
-        <v>-65.27322924491986</v>
+        <v>-66.80868125997326</v>
       </c>
       <c r="P58">
-        <v>-198.1885291550801</v>
+        <v>-202.8506085400268</v>
       </c>
       <c r="Q58">
-        <v>-107.4885291550801</v>
+        <v>-112.1506085400268</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1169545183857162</v>
+        <v>0.1186092746272445</v>
       </c>
       <c r="T58">
-        <v>1.643291417683976</v>
+        <v>1.681507497164999</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0596783802789317</v>
+        <v>0.05863139115123114</v>
       </c>
       <c r="W58">
-        <v>0.2217278379302279</v>
+        <v>0.2219747179665397</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2408793189586975</v>
+        <v>0.2366533659945098</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1775275773306428</v>
+        <v>0.1794275773306428</v>
       </c>
       <c r="C59">
-        <v>-700.1439898944124</v>
+        <v>-734.8356981988394</v>
       </c>
       <c r="D59">
-        <v>591.3870101055879</v>
+        <v>582.9783018011608</v>
       </c>
       <c r="E59">
-        <v>1458.831</v>
+        <v>1485.114</v>
       </c>
       <c r="F59">
-        <v>1498.131</v>
+        <v>1524.414</v>
       </c>
       <c r="G59">
         <v>206.6</v>
@@ -6125,37 +6125,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M59">
-        <v>353.2592898000001</v>
+        <v>359.4568212000001</v>
       </c>
       <c r="N59">
-        <v>-269.6592898000001</v>
+        <v>-275.8568212000001</v>
       </c>
       <c r="O59">
-        <v>-66.80868125997326</v>
+        <v>-68.34413327502665</v>
       </c>
       <c r="P59">
-        <v>-202.8506085400268</v>
+        <v>-207.5126879249734</v>
       </c>
       <c r="Q59">
-        <v>-112.1506085400268</v>
+        <v>-116.8126879249734</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1186092746272445</v>
+        <v>0.120342828785036</v>
       </c>
       <c r="T59">
-        <v>1.681507497164999</v>
+        <v>1.721543389954642</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05863139115123114</v>
+        <v>0.05762050509689957</v>
       </c>
       <c r="W59">
-        <v>0.2219747179665397</v>
+        <v>0.2222130848981511</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2366533659945098</v>
+        <v>0.2325731355463286</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1794275773306427</v>
+        <v>0.1813275773306427</v>
       </c>
       <c r="C60">
-        <v>-734.8356981988388</v>
+        <v>-769.2916383136017</v>
       </c>
       <c r="D60">
-        <v>582.9783018011611</v>
+        <v>574.8053616863984</v>
       </c>
       <c r="E60">
-        <v>1485.114</v>
+        <v>1511.397</v>
       </c>
       <c r="F60">
-        <v>1524.414</v>
+        <v>1550.697</v>
       </c>
       <c r="G60">
         <v>206.6</v>
@@ -6207,37 +6207,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M60">
-        <v>359.4568212</v>
+        <v>365.6543526</v>
       </c>
       <c r="N60">
-        <v>-275.8568212</v>
+        <v>-282.0543526</v>
       </c>
       <c r="O60">
-        <v>-68.34413327502664</v>
+        <v>-69.87958529008003</v>
       </c>
       <c r="P60">
-        <v>-207.5126879249734</v>
+        <v>-212.17476730992</v>
       </c>
       <c r="Q60">
-        <v>-116.8126879249734</v>
+        <v>-121.47476730992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.120342828785036</v>
+        <v>0.1221609465602808</v>
       </c>
       <c r="T60">
-        <v>1.721543389954642</v>
+        <v>1.763532253124267</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05762050509689957</v>
+        <v>0.05664388636644365</v>
       </c>
       <c r="W60">
-        <v>0.2222130848981511</v>
+        <v>0.2224433715947926</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2325731355463286</v>
+        <v>0.228631217994696</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1813275773306427</v>
+        <v>0.1832275773306427</v>
       </c>
       <c r="C61">
-        <v>-769.2916383136017</v>
+        <v>-803.5215890524373</v>
       </c>
       <c r="D61">
-        <v>574.8053616863984</v>
+        <v>566.8584109475627</v>
       </c>
       <c r="E61">
-        <v>1511.397</v>
+        <v>1537.68</v>
       </c>
       <c r="F61">
-        <v>1550.697</v>
+        <v>1576.98</v>
       </c>
       <c r="G61">
         <v>206.6</v>
@@ -6289,37 +6289,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M61">
-        <v>365.6543526</v>
+        <v>371.851884</v>
       </c>
       <c r="N61">
-        <v>-282.0543526</v>
+        <v>-288.251884</v>
       </c>
       <c r="O61">
-        <v>-69.87958529008003</v>
+        <v>-71.41503730513341</v>
       </c>
       <c r="P61">
-        <v>-212.17476730992</v>
+        <v>-216.8368466948666</v>
       </c>
       <c r="Q61">
-        <v>-121.47476730992</v>
+        <v>-126.1368466948666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1221609465602808</v>
+        <v>0.1240699702242878</v>
       </c>
       <c r="T61">
-        <v>1.763532253124267</v>
+        <v>1.807620559452374</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05664388636644365</v>
+        <v>0.05569982159366959</v>
       </c>
       <c r="W61">
-        <v>0.2224433715947926</v>
+        <v>0.2226659820682127</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.228631217994696</v>
+        <v>0.2248206976947843</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1832275773306427</v>
+        <v>0.1851275773306428</v>
       </c>
       <c r="C62">
-        <v>-803.5215890524373</v>
+        <v>-837.5347958172076</v>
       </c>
       <c r="D62">
-        <v>566.8584109475627</v>
+        <v>559.1282041827925</v>
       </c>
       <c r="E62">
-        <v>1537.68</v>
+        <v>1563.963</v>
       </c>
       <c r="F62">
-        <v>1576.98</v>
+        <v>1603.263</v>
       </c>
       <c r="G62">
         <v>206.6</v>
@@ -6371,37 +6371,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M62">
-        <v>371.851884</v>
+        <v>378.0494154</v>
       </c>
       <c r="N62">
-        <v>-288.251884</v>
+        <v>-294.4494154</v>
       </c>
       <c r="O62">
-        <v>-71.41503730513341</v>
+        <v>-72.9504893201868</v>
       </c>
       <c r="P62">
-        <v>-216.8368466948666</v>
+        <v>-221.4989260798132</v>
       </c>
       <c r="Q62">
-        <v>-126.1368466948666</v>
+        <v>-130.7989260798132</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1240699702242878</v>
+        <v>0.1260768925377311</v>
       </c>
       <c r="T62">
-        <v>1.807620559452374</v>
+        <v>1.853969804566537</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05569982159366959</v>
+        <v>0.05478670976426517</v>
       </c>
       <c r="W62">
-        <v>0.2226659820682127</v>
+        <v>0.2228812938375863</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2248206976947843</v>
+        <v>0.2211351124866732</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1851275773306428</v>
+        <v>0.1870275773306428</v>
       </c>
       <c r="C63">
-        <v>-837.5347958172076</v>
+        <v>-871.3400064790824</v>
       </c>
       <c r="D63">
-        <v>559.1282041827925</v>
+        <v>551.6059935209177</v>
       </c>
       <c r="E63">
-        <v>1563.963</v>
+        <v>1590.246</v>
       </c>
       <c r="F63">
-        <v>1603.263</v>
+        <v>1629.546</v>
       </c>
       <c r="G63">
         <v>206.6</v>
@@ -6453,37 +6453,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M63">
-        <v>378.0494154</v>
+        <v>384.2469468</v>
       </c>
       <c r="N63">
-        <v>-294.4494154</v>
+        <v>-300.6469468</v>
       </c>
       <c r="O63">
-        <v>-72.9504893201868</v>
+        <v>-74.4859413352402</v>
       </c>
       <c r="P63">
-        <v>-221.4989260798132</v>
+        <v>-226.1610054647598</v>
       </c>
       <c r="Q63">
-        <v>-130.7989260798132</v>
+        <v>-135.4610054647598</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1260768925377311</v>
+        <v>0.1281894423413556</v>
       </c>
       <c r="T63">
-        <v>1.853969804566537</v>
+        <v>1.902758483634078</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05478670976426517</v>
+        <v>0.05390305315516412</v>
       </c>
       <c r="W63">
-        <v>0.2228812938375863</v>
+        <v>0.2230896600660123</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2211351124866732</v>
+        <v>0.2175684171239849</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1870275773306428</v>
+        <v>0.1889275773306427</v>
       </c>
       <c r="C64">
-        <v>-871.3400064790824</v>
+        <v>-904.9455044018177</v>
       </c>
       <c r="D64">
-        <v>551.6059935209177</v>
+        <v>544.2834955981824</v>
       </c>
       <c r="E64">
-        <v>1590.246</v>
+        <v>1616.529</v>
       </c>
       <c r="F64">
-        <v>1629.546</v>
+        <v>1655.829</v>
       </c>
       <c r="G64">
         <v>206.6</v>
@@ -6535,37 +6535,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M64">
-        <v>384.2469468</v>
+        <v>390.4444782</v>
       </c>
       <c r="N64">
-        <v>-300.6469468</v>
+        <v>-306.8444782</v>
       </c>
       <c r="O64">
-        <v>-74.4859413352402</v>
+        <v>-76.02139335029358</v>
       </c>
       <c r="P64">
-        <v>-226.1610054647598</v>
+        <v>-230.8230848497064</v>
       </c>
       <c r="Q64">
-        <v>-135.4610054647598</v>
+        <v>-140.1230848497065</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1281894423413556</v>
+        <v>0.1304161840262571</v>
       </c>
       <c r="T64">
-        <v>1.902758483634078</v>
+        <v>1.954184388597161</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05390305315516412</v>
+        <v>0.05304744913682818</v>
       </c>
       <c r="W64">
-        <v>0.2230896600660123</v>
+        <v>0.2232914114935359</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2175684171239849</v>
+        <v>0.2141149501855089</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1889275773306427</v>
+        <v>0.1908275773306427</v>
       </c>
       <c r="C65">
-        <v>-904.9455044018177</v>
+        <v>-938.3591388692115</v>
       </c>
       <c r="D65">
-        <v>544.2834955981824</v>
+        <v>537.1528611307886</v>
       </c>
       <c r="E65">
-        <v>1616.529</v>
+        <v>1642.812</v>
       </c>
       <c r="F65">
-        <v>1655.829</v>
+        <v>1682.112</v>
       </c>
       <c r="G65">
         <v>206.6</v>
@@ -6617,37 +6617,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M65">
-        <v>390.4444782</v>
+        <v>396.6420096000001</v>
       </c>
       <c r="N65">
-        <v>-306.8444782</v>
+        <v>-313.0420096</v>
       </c>
       <c r="O65">
-        <v>-76.02139335029358</v>
+        <v>-77.55684536534697</v>
       </c>
       <c r="P65">
-        <v>-230.8230848497064</v>
+        <v>-235.485164234653</v>
       </c>
       <c r="Q65">
-        <v>-140.1230848497065</v>
+        <v>-144.7851642346531</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1304161840262571</v>
+        <v>0.132766633582542</v>
       </c>
       <c r="T65">
-        <v>1.954184388597161</v>
+        <v>2.008467288280415</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05304744913682818</v>
+        <v>0.05221858274406524</v>
       </c>
       <c r="W65">
-        <v>0.2232914114935359</v>
+        <v>0.2234868581889494</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2141149501855089</v>
+        <v>0.2107694040888604</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1908275773306427</v>
+        <v>0.1927275773306427</v>
       </c>
       <c r="C66">
-        <v>-938.3591388692115</v>
+        <v>-971.5883531517203</v>
       </c>
       <c r="D66">
-        <v>537.1528611307886</v>
+        <v>530.2066468482799</v>
       </c>
       <c r="E66">
-        <v>1642.812</v>
+        <v>1669.095</v>
       </c>
       <c r="F66">
-        <v>1682.112</v>
+        <v>1708.395</v>
       </c>
       <c r="G66">
         <v>206.6</v>
@@ -6699,37 +6699,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M66">
-        <v>396.6420096000001</v>
+        <v>402.8395410000001</v>
       </c>
       <c r="N66">
-        <v>-313.0420096</v>
+        <v>-319.239541</v>
       </c>
       <c r="O66">
-        <v>-77.55684536534697</v>
+        <v>-79.09229738040037</v>
       </c>
       <c r="P66">
-        <v>-235.485164234653</v>
+        <v>-240.1472436195997</v>
       </c>
       <c r="Q66">
-        <v>-144.7851642346531</v>
+        <v>-149.4472436195996</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.132766633582542</v>
+        <v>0.1352513945420432</v>
       </c>
       <c r="T66">
-        <v>2.008467288280415</v>
+        <v>2.06585206794557</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05221858274406524</v>
+        <v>0.05141521993261809</v>
       </c>
       <c r="W66">
-        <v>0.2234868581889494</v>
+        <v>0.2236762911398887</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2107694040888604</v>
+        <v>0.2075267978721086</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1927275773306427</v>
+        <v>0.1946275773306428</v>
       </c>
       <c r="C67">
-        <v>-971.5883531517203</v>
+        <v>-1004.640210423203</v>
       </c>
       <c r="D67">
-        <v>530.2066468482799</v>
+        <v>523.4377895767967</v>
       </c>
       <c r="E67">
-        <v>1669.095</v>
+        <v>1695.378</v>
       </c>
       <c r="F67">
-        <v>1708.395</v>
+        <v>1734.678</v>
       </c>
       <c r="G67">
         <v>206.6</v>
@@ -6781,37 +6781,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M67">
-        <v>402.8395410000001</v>
+        <v>409.0370724000001</v>
       </c>
       <c r="N67">
-        <v>-319.239541</v>
+        <v>-325.4370724</v>
       </c>
       <c r="O67">
-        <v>-79.09229738040037</v>
+        <v>-80.62774939545375</v>
       </c>
       <c r="P67">
-        <v>-240.1472436195997</v>
+        <v>-244.8093230045463</v>
       </c>
       <c r="Q67">
-        <v>-149.4472436195996</v>
+        <v>-154.1093230045463</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1352513945420432</v>
+        <v>0.1378823179109268</v>
       </c>
       <c r="T67">
-        <v>2.06585206794557</v>
+        <v>2.126612422885146</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05141521993261809</v>
+        <v>0.05063620144879054</v>
       </c>
       <c r="W67">
-        <v>0.2236762911398887</v>
+        <v>0.2238599836983752</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2075267978721086</v>
+        <v>0.2043824524498039</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1946275773306428</v>
+        <v>0.1965275773306428</v>
       </c>
       <c r="C68">
-        <v>-1004.640210423203</v>
+        <v>-1037.521417717508</v>
       </c>
       <c r="D68">
-        <v>523.4377895767967</v>
+        <v>516.8395822824922</v>
       </c>
       <c r="E68">
-        <v>1695.378</v>
+        <v>1721.661</v>
       </c>
       <c r="F68">
-        <v>1734.678</v>
+        <v>1760.961</v>
       </c>
       <c r="G68">
         <v>206.6</v>
@@ -6863,37 +6863,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M68">
-        <v>409.0370724000001</v>
+        <v>415.2346038000001</v>
       </c>
       <c r="N68">
-        <v>-325.4370724</v>
+        <v>-331.6346038</v>
       </c>
       <c r="O68">
-        <v>-80.62774939545375</v>
+        <v>-82.16320141050714</v>
       </c>
       <c r="P68">
-        <v>-244.8093230045463</v>
+        <v>-249.4714023894929</v>
       </c>
       <c r="Q68">
-        <v>-154.1093230045463</v>
+        <v>-158.7714023894929</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1378823179109268</v>
+        <v>0.1406726911809549</v>
       </c>
       <c r="T68">
-        <v>2.126612422885146</v>
+        <v>2.191055223578635</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05063620144879054</v>
+        <v>0.04988043724806232</v>
       </c>
       <c r="W68">
-        <v>0.2238599836983752</v>
+        <v>0.2240381928969069</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2043824524498039</v>
+        <v>0.2013319680848815</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1965275773306428</v>
+        <v>0.1984275773306427</v>
       </c>
       <c r="C69">
-        <v>-1037.521417717508</v>
+        <v>-1070.238348095695</v>
       </c>
       <c r="D69">
-        <v>516.8395822824922</v>
+        <v>510.4056519043052</v>
       </c>
       <c r="E69">
-        <v>1721.661</v>
+        <v>1747.944</v>
       </c>
       <c r="F69">
-        <v>1760.961</v>
+        <v>1787.244</v>
       </c>
       <c r="G69">
         <v>206.6</v>
@@ -6945,37 +6945,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M69">
-        <v>415.2346038000001</v>
+        <v>421.4321352000001</v>
       </c>
       <c r="N69">
-        <v>-331.6346038</v>
+        <v>-337.8321352</v>
       </c>
       <c r="O69">
-        <v>-82.16320141050714</v>
+        <v>-83.69865342556054</v>
       </c>
       <c r="P69">
-        <v>-249.4714023894929</v>
+        <v>-254.1334817744395</v>
       </c>
       <c r="Q69">
-        <v>-158.7714023894929</v>
+        <v>-163.4334817744395</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1406726911809549</v>
+        <v>0.1436374627803597</v>
       </c>
       <c r="T69">
-        <v>2.191055223578635</v>
+        <v>2.259525699315467</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04988043724806232</v>
+        <v>0.04914690140617905</v>
       </c>
       <c r="W69">
-        <v>0.2240381928969069</v>
+        <v>0.224211160648423</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2013319680848815</v>
+        <v>0.1983712038483391</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1984275773306427</v>
+        <v>0.2003275773306428</v>
       </c>
       <c r="C70">
-        <v>-1070.238348095695</v>
+        <v>-1102.797061177919</v>
       </c>
       <c r="D70">
-        <v>510.4056519043052</v>
+        <v>504.1299388220816</v>
       </c>
       <c r="E70">
-        <v>1747.944</v>
+        <v>1774.227</v>
       </c>
       <c r="F70">
-        <v>1787.244</v>
+        <v>1813.527</v>
       </c>
       <c r="G70">
         <v>206.6</v>
@@ -7027,37 +7027,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M70">
-        <v>421.4321352000001</v>
+        <v>427.6296666000001</v>
       </c>
       <c r="N70">
-        <v>-337.8321352</v>
+        <v>-344.0296666</v>
       </c>
       <c r="O70">
-        <v>-83.69865342556054</v>
+        <v>-85.23410544061392</v>
       </c>
       <c r="P70">
-        <v>-254.1334817744395</v>
+        <v>-258.7955611593861</v>
       </c>
       <c r="Q70">
-        <v>-163.4334817744395</v>
+        <v>-168.0955611593861</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1436374627803597</v>
+        <v>0.146793509966823</v>
       </c>
       <c r="T70">
-        <v>2.259525699315467</v>
+        <v>2.332413625099838</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04914690140617905</v>
+        <v>0.04843462747275617</v>
       </c>
       <c r="W70">
-        <v>0.224211160648423</v>
+        <v>0.2243791148419241</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1983712038483391</v>
+        <v>0.1954962588650299</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2003275773306428</v>
+        <v>0.2022275773306428</v>
       </c>
       <c r="C71">
-        <v>-1102.797061177919</v>
+        <v>-1135.203322178997</v>
       </c>
       <c r="D71">
-        <v>504.1299388220816</v>
+        <v>498.0066778210029</v>
       </c>
       <c r="E71">
-        <v>1774.227</v>
+        <v>1800.51</v>
       </c>
       <c r="F71">
-        <v>1813.527</v>
+        <v>1839.81</v>
       </c>
       <c r="G71">
         <v>206.6</v>
@@ -7109,37 +7109,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M71">
-        <v>427.6296666000001</v>
+        <v>433.8271980000001</v>
       </c>
       <c r="N71">
-        <v>-344.0296666</v>
+        <v>-350.2271980000001</v>
       </c>
       <c r="O71">
-        <v>-85.23410544061392</v>
+        <v>-86.76955745566733</v>
       </c>
       <c r="P71">
-        <v>-258.7955611593861</v>
+        <v>-263.4576405443328</v>
       </c>
       <c r="Q71">
-        <v>-168.0955611593861</v>
+        <v>-172.7576405443328</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.146793509966823</v>
+        <v>0.1501599602990504</v>
       </c>
       <c r="T71">
-        <v>2.332413625099838</v>
+        <v>2.410160745936499</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04843462747275617</v>
+        <v>0.04774270422314535</v>
       </c>
       <c r="W71">
-        <v>0.2243791148419241</v>
+        <v>0.2245422703441823</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1954962588650299</v>
+        <v>0.192703455166958</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2022275773306428</v>
+        <v>0.2041275773306428</v>
       </c>
       <c r="C72">
-        <v>-1135.203322178997</v>
+        <v>-1167.462619573379</v>
       </c>
       <c r="D72">
-        <v>498.0066778210029</v>
+        <v>492.0303804266213</v>
       </c>
       <c r="E72">
-        <v>1800.51</v>
+        <v>1826.793</v>
       </c>
       <c r="F72">
-        <v>1839.81</v>
+        <v>1866.093</v>
       </c>
       <c r="G72">
         <v>206.6</v>
@@ -7191,37 +7191,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M72">
-        <v>433.8271980000001</v>
+        <v>440.0247294000001</v>
       </c>
       <c r="N72">
-        <v>-350.2271980000001</v>
+        <v>-356.4247294</v>
       </c>
       <c r="O72">
-        <v>-86.76955745566733</v>
+        <v>-88.30500947072071</v>
       </c>
       <c r="P72">
-        <v>-263.4576405443328</v>
+        <v>-268.1197199292793</v>
       </c>
       <c r="Q72">
-        <v>-172.7576405443328</v>
+        <v>-177.4197199292793</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1501599602990504</v>
+        <v>0.1537585796197073</v>
       </c>
       <c r="T72">
-        <v>2.410160745936499</v>
+        <v>2.493269737175689</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04774270422314535</v>
+        <v>0.04707027176929824</v>
       </c>
       <c r="W72">
-        <v>0.2245422703441823</v>
+        <v>0.2247008299167995</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.192703455166958</v>
+        <v>0.1899893219955924</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2041275773306427</v>
+        <v>0.2060275773306427</v>
       </c>
       <c r="C73">
-        <v>-1167.462619573379</v>
+        <v>-1199.580181503261</v>
       </c>
       <c r="D73">
-        <v>492.030380426621</v>
+        <v>486.1958184967394</v>
       </c>
       <c r="E73">
-        <v>1826.793</v>
+        <v>1853.076</v>
       </c>
       <c r="F73">
-        <v>1866.093</v>
+        <v>1892.376</v>
       </c>
       <c r="G73">
         <v>206.6</v>
@@ -7273,37 +7273,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M73">
-        <v>440.0247294</v>
+        <v>446.2222608</v>
       </c>
       <c r="N73">
-        <v>-356.4247294</v>
+        <v>-362.6222608</v>
       </c>
       <c r="O73">
-        <v>-88.30500947072069</v>
+        <v>-89.84046148577407</v>
       </c>
       <c r="P73">
-        <v>-268.1197199292793</v>
+        <v>-272.7817993142259</v>
       </c>
       <c r="Q73">
-        <v>-177.4197199292793</v>
+        <v>-182.0817993142259</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1537585796197073</v>
+        <v>0.157614243177554</v>
       </c>
       <c r="T73">
-        <v>2.493269737175688</v>
+        <v>2.582315084931962</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04707027176929825</v>
+        <v>0.04641651799472467</v>
       </c>
       <c r="W73">
-        <v>0.2247008299167995</v>
+        <v>0.2248549850568439</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1899893219955924</v>
+        <v>0.1873505814123203</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2060275773306427</v>
+        <v>0.2079275773306427</v>
       </c>
       <c r="C74">
-        <v>-1199.580181503261</v>
+        <v>-1231.560991032974</v>
       </c>
       <c r="D74">
-        <v>486.1958184967394</v>
+        <v>480.4980089670262</v>
       </c>
       <c r="E74">
-        <v>1853.076</v>
+        <v>1879.359</v>
       </c>
       <c r="F74">
-        <v>1892.376</v>
+        <v>1918.659</v>
       </c>
       <c r="G74">
         <v>206.6</v>
@@ -7355,37 +7355,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M74">
-        <v>446.2222608</v>
+        <v>452.4197922</v>
       </c>
       <c r="N74">
-        <v>-362.6222608</v>
+        <v>-368.8197922</v>
       </c>
       <c r="O74">
-        <v>-89.84046148577407</v>
+        <v>-91.37591350082747</v>
       </c>
       <c r="P74">
-        <v>-272.7817993142259</v>
+        <v>-277.4438786991725</v>
       </c>
       <c r="Q74">
-        <v>-182.0817993142259</v>
+        <v>-186.7438786991725</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.157614243177554</v>
+        <v>0.1617555114433893</v>
       </c>
       <c r="T74">
-        <v>2.582315084931962</v>
+        <v>2.677956384373887</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04641651799472467</v>
+        <v>0.04578067528246816</v>
       </c>
       <c r="W74">
-        <v>0.2248549850568439</v>
+        <v>0.225004916768394</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1873505814123203</v>
+        <v>0.1847841350916036</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2079275773306427</v>
+        <v>0.2098275773306427</v>
       </c>
       <c r="C75">
-        <v>-1231.560991032974</v>
+        <v>-1263.40980034318</v>
       </c>
       <c r="D75">
-        <v>480.4980089670262</v>
+        <v>474.9321996568206</v>
       </c>
       <c r="E75">
-        <v>1879.359</v>
+        <v>1905.642</v>
       </c>
       <c r="F75">
-        <v>1918.659</v>
+        <v>1944.942</v>
       </c>
       <c r="G75">
         <v>206.6</v>
@@ -7437,37 +7437,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M75">
-        <v>452.4197922</v>
+        <v>458.6173236</v>
       </c>
       <c r="N75">
-        <v>-368.8197922</v>
+        <v>-375.0173236</v>
       </c>
       <c r="O75">
-        <v>-91.37591350082747</v>
+        <v>-92.91136551588086</v>
       </c>
       <c r="P75">
-        <v>-277.4438786991725</v>
+        <v>-282.1059580841192</v>
       </c>
       <c r="Q75">
-        <v>-186.7438786991725</v>
+        <v>-191.4059580841192</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1617555114433893</v>
+        <v>0.1662153388065966</v>
       </c>
       <c r="T75">
-        <v>2.677956384373887</v>
+        <v>2.780954706849805</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04578067528246816</v>
+        <v>0.04516201750838075</v>
       </c>
       <c r="W75">
-        <v>0.225004916768394</v>
+        <v>0.2251507962715238</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1847841350916036</v>
+        <v>0.1822870521849603</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2098275773306427</v>
+        <v>0.2117275773306428</v>
       </c>
       <c r="C76">
-        <v>-1263.40980034318</v>
+        <v>-1295.131143949859</v>
       </c>
       <c r="D76">
-        <v>474.9321996568206</v>
+        <v>469.4938560501411</v>
       </c>
       <c r="E76">
-        <v>1905.642</v>
+        <v>1931.925</v>
       </c>
       <c r="F76">
-        <v>1944.942</v>
+        <v>1971.225</v>
       </c>
       <c r="G76">
         <v>206.6</v>
@@ -7519,37 +7519,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M76">
-        <v>458.6173236</v>
+        <v>464.814855</v>
       </c>
       <c r="N76">
-        <v>-375.0173236</v>
+        <v>-381.214855</v>
       </c>
       <c r="O76">
-        <v>-92.91136551588086</v>
+        <v>-94.44681753093424</v>
       </c>
       <c r="P76">
-        <v>-282.1059580841192</v>
+        <v>-286.7680374690657</v>
       </c>
       <c r="Q76">
-        <v>-191.4059580841192</v>
+        <v>-196.0680374690658</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1662153388065966</v>
+        <v>0.1710319523588605</v>
       </c>
       <c r="T76">
-        <v>2.780954706849805</v>
+        <v>2.892192895123798</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04516201750838075</v>
+        <v>0.04455985727493568</v>
       </c>
       <c r="W76">
-        <v>0.2251507962715238</v>
+        <v>0.2252927856545702</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1822870521849603</v>
+        <v>0.1798565581558275</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2117275773306428</v>
+        <v>0.2136275773306427</v>
       </c>
       <c r="C77">
-        <v>-1295.131143949859</v>
+        <v>-1326.72935102538</v>
       </c>
       <c r="D77">
-        <v>469.4938560501411</v>
+        <v>464.1786489746206</v>
       </c>
       <c r="E77">
-        <v>1931.925</v>
+        <v>1958.208</v>
       </c>
       <c r="F77">
-        <v>1971.225</v>
+        <v>1997.508</v>
       </c>
       <c r="G77">
         <v>206.6</v>
@@ -7601,37 +7601,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M77">
-        <v>464.814855</v>
+        <v>471.0123864000001</v>
       </c>
       <c r="N77">
-        <v>-381.214855</v>
+        <v>-387.4123864000001</v>
       </c>
       <c r="O77">
-        <v>-94.44681753093424</v>
+        <v>-95.98226954598765</v>
       </c>
       <c r="P77">
-        <v>-286.7680374690657</v>
+        <v>-291.4301168540124</v>
       </c>
       <c r="Q77">
-        <v>-196.0680374690658</v>
+        <v>-200.7301168540124</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1710319523588605</v>
+        <v>0.176249950373813</v>
       </c>
       <c r="T77">
-        <v>2.892192895123798</v>
+        <v>3.012700932420623</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04455985727493568</v>
+        <v>0.04397354336342336</v>
       </c>
       <c r="W77">
-        <v>0.2252927856545702</v>
+        <v>0.2254310384749048</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1798565581558275</v>
+        <v>0.1774900244958824</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2136275773306427</v>
+        <v>0.2155275773306428</v>
       </c>
       <c r="C78">
-        <v>-1326.72935102538</v>
+        <v>-1358.208556891994</v>
       </c>
       <c r="D78">
-        <v>464.1786489746206</v>
+        <v>458.9824431080057</v>
       </c>
       <c r="E78">
-        <v>1958.208</v>
+        <v>1984.491</v>
       </c>
       <c r="F78">
-        <v>1997.508</v>
+        <v>2023.791</v>
       </c>
       <c r="G78">
         <v>206.6</v>
@@ -7683,37 +7683,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M78">
-        <v>471.0123864000001</v>
+        <v>477.2099178000001</v>
       </c>
       <c r="N78">
-        <v>-387.4123864000001</v>
+        <v>-393.6099178000001</v>
       </c>
       <c r="O78">
-        <v>-95.98226954598765</v>
+        <v>-97.51772156104104</v>
       </c>
       <c r="P78">
-        <v>-291.4301168540124</v>
+        <v>-296.092196238959</v>
       </c>
       <c r="Q78">
-        <v>-200.7301168540124</v>
+        <v>-205.392196238959</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.176249950373813</v>
+        <v>0.1819216873465875</v>
       </c>
       <c r="T78">
-        <v>3.012700932420623</v>
+        <v>3.143687929482389</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04397354336342336</v>
+        <v>0.0434024583846776</v>
       </c>
       <c r="W78">
-        <v>0.2254310384749048</v>
+        <v>0.225565700312893</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1774900244958824</v>
+        <v>0.1751849592426891</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2155275773306428</v>
+        <v>0.2174275773306427</v>
       </c>
       <c r="C79">
-        <v>-1358.208556891994</v>
+        <v>-1389.572713751915</v>
       </c>
       <c r="D79">
-        <v>458.9824431080057</v>
+        <v>453.9012862480854</v>
       </c>
       <c r="E79">
-        <v>1984.491</v>
+        <v>2010.774</v>
       </c>
       <c r="F79">
-        <v>2023.791</v>
+        <v>2050.074</v>
       </c>
       <c r="G79">
         <v>206.6</v>
@@ -7765,37 +7765,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M79">
-        <v>477.2099178000001</v>
+        <v>483.4074492</v>
       </c>
       <c r="N79">
-        <v>-393.6099178000001</v>
+        <v>-399.8074492</v>
       </c>
       <c r="O79">
-        <v>-97.51772156104104</v>
+        <v>-99.05317357609441</v>
       </c>
       <c r="P79">
-        <v>-296.092196238959</v>
+        <v>-300.7542756239056</v>
       </c>
       <c r="Q79">
-        <v>-205.392196238959</v>
+        <v>-210.0542756239056</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1819216873465875</v>
+        <v>0.1881090367714323</v>
       </c>
       <c r="T79">
-        <v>3.143687929482389</v>
+        <v>3.286582835367953</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0434024583846776</v>
+        <v>0.04284601661051507</v>
       </c>
       <c r="W79">
-        <v>0.225565700312893</v>
+        <v>0.2256969092832405</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1751849592426891</v>
+        <v>0.1729389982267572</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2174275773306427</v>
+        <v>0.2193275773306428</v>
       </c>
       <c r="C80">
-        <v>-1389.572713751915</v>
+        <v>-1420.825600712465</v>
       </c>
       <c r="D80">
-        <v>453.9012862480854</v>
+        <v>448.9313992875354</v>
       </c>
       <c r="E80">
-        <v>2010.774</v>
+        <v>2037.057</v>
       </c>
       <c r="F80">
-        <v>2050.074</v>
+        <v>2076.357</v>
       </c>
       <c r="G80">
         <v>206.6</v>
@@ -7847,37 +7847,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M80">
-        <v>483.4074492</v>
+        <v>489.6049806000001</v>
       </c>
       <c r="N80">
-        <v>-399.8074492</v>
+        <v>-406.0049806000001</v>
       </c>
       <c r="O80">
-        <v>-99.05317357609441</v>
+        <v>-100.5886255911478</v>
       </c>
       <c r="P80">
-        <v>-300.7542756239056</v>
+        <v>-305.4163550088523</v>
       </c>
       <c r="Q80">
-        <v>-210.0542756239056</v>
+        <v>-214.7163550088523</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1881090367714323</v>
+        <v>0.194885657570072</v>
       </c>
       <c r="T80">
-        <v>3.286582835367953</v>
+        <v>3.443086779909284</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04284601661051507</v>
+        <v>0.04230366196987563</v>
       </c>
       <c r="W80">
-        <v>0.2256969092832405</v>
+        <v>0.2258247965075033</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1729389982267572</v>
+        <v>0.1707498969833805</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2193275773306428</v>
+        <v>0.2212275773306427</v>
       </c>
       <c r="C81">
-        <v>-1420.825600712465</v>
+        <v>-1451.970833159754</v>
       </c>
       <c r="D81">
-        <v>448.9313992875354</v>
+        <v>444.0691668402462</v>
       </c>
       <c r="E81">
-        <v>2037.057</v>
+        <v>2063.34</v>
       </c>
       <c r="F81">
-        <v>2076.357</v>
+        <v>2102.64</v>
       </c>
       <c r="G81">
         <v>206.6</v>
@@ -7929,37 +7929,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M81">
-        <v>489.6049806000001</v>
+        <v>495.8025120000001</v>
       </c>
       <c r="N81">
-        <v>-406.0049806000001</v>
+        <v>-412.2025120000001</v>
       </c>
       <c r="O81">
-        <v>-100.5886255911478</v>
+        <v>-102.1240776062012</v>
       </c>
       <c r="P81">
-        <v>-305.4163550088523</v>
+        <v>-310.0784343937989</v>
       </c>
       <c r="Q81">
-        <v>-214.7163550088523</v>
+        <v>-219.3784343937989</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.194885657570072</v>
+        <v>0.2023399404485756</v>
       </c>
       <c r="T81">
-        <v>3.443086779909284</v>
+        <v>3.615241118904748</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04230366196987563</v>
+        <v>0.04177486619525219</v>
       </c>
       <c r="W81">
-        <v>0.2258247965075033</v>
+        <v>0.2259494865511595</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1707498969833805</v>
+        <v>0.1686155232710882</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2212275773306427</v>
+        <v>0.2231275773306428</v>
       </c>
       <c r="C82">
-        <v>-1451.970833159754</v>
+        <v>-1483.011871529743</v>
       </c>
       <c r="D82">
-        <v>444.0691668402462</v>
+        <v>439.3111284702569</v>
       </c>
       <c r="E82">
-        <v>2063.34</v>
+        <v>2089.623</v>
       </c>
       <c r="F82">
-        <v>2102.64</v>
+        <v>2128.923</v>
       </c>
       <c r="G82">
         <v>206.6</v>
@@ -8011,37 +8011,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M82">
-        <v>495.8025120000001</v>
+        <v>502.0000434000001</v>
       </c>
       <c r="N82">
-        <v>-412.2025120000001</v>
+        <v>-418.4000434000001</v>
       </c>
       <c r="O82">
-        <v>-102.1240776062012</v>
+        <v>-103.6595296212546</v>
       </c>
       <c r="P82">
-        <v>-310.0784343937989</v>
+        <v>-314.7405137787455</v>
       </c>
       <c r="Q82">
-        <v>-219.3784343937989</v>
+        <v>-224.0405137787455</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2023399404485756</v>
+        <v>0.2105788846827112</v>
       </c>
       <c r="T82">
-        <v>3.615241118904748</v>
+        <v>3.805516967268156</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04177486619525219</v>
+        <v>0.04125912710642191</v>
       </c>
       <c r="W82">
-        <v>0.2259494865511595</v>
+        <v>0.2260710978283057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1686155232710882</v>
+        <v>0.1665338501442847</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2231275773306428</v>
+        <v>0.2250275773306428</v>
       </c>
       <c r="C83">
-        <v>-1483.011871529743</v>
+        <v>-1513.952029521416</v>
       </c>
       <c r="D83">
-        <v>439.3111284702569</v>
+        <v>434.6539704785842</v>
       </c>
       <c r="E83">
-        <v>2089.623</v>
+        <v>2115.906</v>
       </c>
       <c r="F83">
-        <v>2128.923</v>
+        <v>2155.206</v>
       </c>
       <c r="G83">
         <v>206.6</v>
@@ -8093,37 +8093,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M83">
-        <v>502.0000434000001</v>
+        <v>508.1975748</v>
       </c>
       <c r="N83">
-        <v>-418.4000434000001</v>
+        <v>-424.5975748</v>
       </c>
       <c r="O83">
-        <v>-103.6595296212546</v>
+        <v>-105.194981636308</v>
       </c>
       <c r="P83">
-        <v>-314.7405137787455</v>
+        <v>-319.402593163692</v>
       </c>
       <c r="Q83">
-        <v>-224.0405137787455</v>
+        <v>-228.702593163692</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2105788846827112</v>
+        <v>0.219733267165084</v>
       </c>
       <c r="T83">
-        <v>3.805516967268156</v>
+        <v>4.016934576560832</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04125912710642191</v>
+        <v>0.04075596701975824</v>
       </c>
       <c r="W83">
-        <v>0.2260710978283057</v>
+        <v>0.226189742976741</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1665338501442847</v>
+        <v>0.164502949532769</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2250275773306428</v>
+        <v>0.2269275773306428</v>
       </c>
       <c r="C84">
-        <v>-1513.952029521416</v>
+        <v>-1544.794481793015</v>
       </c>
       <c r="D84">
-        <v>434.6539704785842</v>
+        <v>430.0945182069859</v>
       </c>
       <c r="E84">
-        <v>2115.906</v>
+        <v>2142.189</v>
       </c>
       <c r="F84">
-        <v>2155.206</v>
+        <v>2181.489</v>
       </c>
       <c r="G84">
         <v>206.6</v>
@@ -8175,37 +8175,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M84">
-        <v>508.1975748</v>
+        <v>514.3951062000001</v>
       </c>
       <c r="N84">
-        <v>-424.5975748</v>
+        <v>-430.7951062000001</v>
       </c>
       <c r="O84">
-        <v>-105.194981636308</v>
+        <v>-106.7304336513614</v>
       </c>
       <c r="P84">
-        <v>-319.402593163692</v>
+        <v>-324.0646725486387</v>
       </c>
       <c r="Q84">
-        <v>-228.702593163692</v>
+        <v>-233.3646725486387</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.219733267165084</v>
+        <v>0.2299646358218537</v>
       </c>
       <c r="T84">
-        <v>4.016934576560832</v>
+        <v>4.253224845770292</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04075596701975824</v>
+        <v>0.04026493127253223</v>
       </c>
       <c r="W84">
-        <v>0.226189742976741</v>
+        <v>0.2263055292059369</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.164502949532769</v>
+        <v>0.1625209862853862</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2269275773306428</v>
+        <v>0.2288275773306428</v>
       </c>
       <c r="C85">
-        <v>-1544.794481793015</v>
+        <v>-1575.542271178917</v>
       </c>
       <c r="D85">
-        <v>430.0945182069859</v>
+        <v>425.629728821084</v>
       </c>
       <c r="E85">
-        <v>2142.189</v>
+        <v>2168.472</v>
       </c>
       <c r="F85">
-        <v>2181.489</v>
+        <v>2207.772</v>
       </c>
       <c r="G85">
         <v>206.6</v>
@@ -8257,37 +8257,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M85">
-        <v>514.3951062000001</v>
+        <v>520.5926376000001</v>
       </c>
       <c r="N85">
-        <v>-430.7951062000001</v>
+        <v>-436.9926376000001</v>
       </c>
       <c r="O85">
-        <v>-106.7304336513614</v>
+        <v>-108.2658856664148</v>
       </c>
       <c r="P85">
-        <v>-324.0646725486387</v>
+        <v>-328.7267519335853</v>
       </c>
       <c r="Q85">
-        <v>-233.3646725486387</v>
+        <v>-238.0267519335853</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2299646358218537</v>
+        <v>0.2414749255607196</v>
       </c>
       <c r="T85">
-        <v>4.253224845770292</v>
+        <v>4.519051398630937</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04026493127253223</v>
+        <v>0.03978558685262114</v>
       </c>
       <c r="W85">
-        <v>0.2263055292059369</v>
+        <v>0.2264185586201519</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1625209862853862</v>
+        <v>0.1605862126391316</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2288275773306427</v>
+        <v>0.2307275773306428</v>
       </c>
       <c r="C86">
-        <v>-1575.542271178916</v>
+        <v>-1606.19831546162</v>
       </c>
       <c r="D86">
-        <v>425.6297288210837</v>
+        <v>421.2566845383798</v>
       </c>
       <c r="E86">
-        <v>2168.472</v>
+        <v>2194.755</v>
       </c>
       <c r="F86">
-        <v>2207.772</v>
+        <v>2234.055</v>
       </c>
       <c r="G86">
         <v>206.6</v>
@@ -8339,37 +8339,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M86">
-        <v>520.5926376</v>
+        <v>526.7901690000001</v>
       </c>
       <c r="N86">
-        <v>-436.9926376</v>
+        <v>-443.1901690000001</v>
       </c>
       <c r="O86">
-        <v>-108.2658856664147</v>
+        <v>-109.8013376814682</v>
       </c>
       <c r="P86">
-        <v>-328.7267519335852</v>
+        <v>-333.3888313185319</v>
       </c>
       <c r="Q86">
-        <v>-238.0267519335852</v>
+        <v>-242.6888313185319</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2414749255607194</v>
+        <v>0.2545199205981007</v>
       </c>
       <c r="T86">
-        <v>4.519051398630934</v>
+        <v>4.820321491872996</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03978558685262115</v>
+        <v>0.03931752112494324</v>
       </c>
       <c r="W86">
-        <v>0.2264185586201519</v>
+        <v>0.2265289285187384</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1605862126391316</v>
+        <v>0.1586969630786713</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2307275773306428</v>
+        <v>0.2326275773306427</v>
       </c>
       <c r="C87">
-        <v>-1606.19831546162</v>
+        <v>-1636.765413730509</v>
       </c>
       <c r="D87">
-        <v>421.2566845383798</v>
+        <v>416.972586269491</v>
       </c>
       <c r="E87">
-        <v>2194.755</v>
+        <v>2221.038</v>
       </c>
       <c r="F87">
-        <v>2234.055</v>
+        <v>2260.338</v>
       </c>
       <c r="G87">
         <v>206.6</v>
@@ -8421,37 +8421,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M87">
-        <v>526.7901690000001</v>
+        <v>532.9877004000001</v>
       </c>
       <c r="N87">
-        <v>-443.1901690000001</v>
+        <v>-449.3877004000001</v>
       </c>
       <c r="O87">
-        <v>-109.8013376814682</v>
+        <v>-111.3367896965215</v>
       </c>
       <c r="P87">
-        <v>-333.3888313185319</v>
+        <v>-338.0509107034786</v>
       </c>
       <c r="Q87">
-        <v>-242.6888313185319</v>
+        <v>-247.3509107034786</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2545199205981007</v>
+        <v>0.2694284863551079</v>
       </c>
       <c r="T87">
-        <v>4.820321491872996</v>
+        <v>5.164630169863925</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03931752112494324</v>
+        <v>0.03886034064674622</v>
       </c>
       <c r="W87">
-        <v>0.2265289285187384</v>
+        <v>0.2266367316754972</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1586969630786713</v>
+        <v>0.1568516495545007</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2326275773306427</v>
+        <v>0.2345275773306427</v>
       </c>
       <c r="C88">
-        <v>-1636.765413730509</v>
+        <v>-1667.24625235652</v>
       </c>
       <c r="D88">
-        <v>416.972586269491</v>
+        <v>412.7747476434799</v>
       </c>
       <c r="E88">
-        <v>2221.038</v>
+        <v>2247.321</v>
       </c>
       <c r="F88">
-        <v>2260.338</v>
+        <v>2286.621</v>
       </c>
       <c r="G88">
         <v>206.6</v>
@@ -8503,37 +8503,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M88">
-        <v>532.9877004000001</v>
+        <v>539.1852318</v>
       </c>
       <c r="N88">
-        <v>-449.3877004000001</v>
+        <v>-455.5852318</v>
       </c>
       <c r="O88">
-        <v>-111.3367896965215</v>
+        <v>-112.8722417115749</v>
       </c>
       <c r="P88">
-        <v>-338.0509107034786</v>
+        <v>-342.712990088425</v>
       </c>
       <c r="Q88">
-        <v>-247.3509107034786</v>
+        <v>-252.0129900884251</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2694284863551079</v>
+        <v>0.2866306776131931</v>
       </c>
       <c r="T88">
-        <v>5.164630169863925</v>
+        <v>5.561909413699611</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03886034064674622</v>
+        <v>0.03841367006459973</v>
       </c>
       <c r="W88">
-        <v>0.2266367316754972</v>
+        <v>0.2267420565987674</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1568516495545007</v>
+        <v>0.1550487570308857</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2345275773306427</v>
+        <v>0.2364275773306427</v>
       </c>
       <c r="C89">
-        <v>-1667.24625235652</v>
+        <v>-1697.643410609512</v>
       </c>
       <c r="D89">
-        <v>412.7747476434799</v>
+        <v>408.6605893904885</v>
       </c>
       <c r="E89">
-        <v>2247.321</v>
+        <v>2273.604</v>
       </c>
       <c r="F89">
-        <v>2286.621</v>
+        <v>2312.904</v>
       </c>
       <c r="G89">
         <v>206.6</v>
@@ -8585,37 +8585,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M89">
-        <v>539.1852318</v>
+        <v>545.3827632</v>
       </c>
       <c r="N89">
-        <v>-455.5852318</v>
+        <v>-461.7827632</v>
       </c>
       <c r="O89">
-        <v>-112.8722417115749</v>
+        <v>-114.4076937266283</v>
       </c>
       <c r="P89">
-        <v>-342.712990088425</v>
+        <v>-347.3750694733717</v>
       </c>
       <c r="Q89">
-        <v>-252.0129900884251</v>
+        <v>-256.6750694733717</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2866306776131931</v>
+        <v>0.3066999007476259</v>
       </c>
       <c r="T89">
-        <v>5.561909413699611</v>
+        <v>6.025401864841245</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03841367006459973</v>
+        <v>0.03797715108659291</v>
       </c>
       <c r="W89">
-        <v>0.2267420565987674</v>
+        <v>0.2268449877737814</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1550487570308857</v>
+        <v>0.153286839337353</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2364275773306427</v>
+        <v>0.2383275773306428</v>
       </c>
       <c r="C90">
-        <v>-1697.643410609512</v>
+        <v>-1727.959365943014</v>
       </c>
       <c r="D90">
-        <v>408.6605893904885</v>
+        <v>404.6276340569863</v>
       </c>
       <c r="E90">
-        <v>2273.604</v>
+        <v>2299.887</v>
       </c>
       <c r="F90">
-        <v>2312.904</v>
+        <v>2339.187</v>
       </c>
       <c r="G90">
         <v>206.6</v>
@@ -8667,37 +8667,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M90">
-        <v>545.3827632</v>
+        <v>551.5802946000001</v>
       </c>
       <c r="N90">
-        <v>-461.7827632</v>
+        <v>-467.9802946000001</v>
       </c>
       <c r="O90">
-        <v>-114.4076937266283</v>
+        <v>-115.9431457416817</v>
       </c>
       <c r="P90">
-        <v>-347.3750694733717</v>
+        <v>-352.0371488583184</v>
       </c>
       <c r="Q90">
-        <v>-256.6750694733717</v>
+        <v>-261.3371488583184</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3066999007476259</v>
+        <v>0.3304180735428647</v>
       </c>
       <c r="T90">
-        <v>6.025401864841245</v>
+        <v>6.573165670735905</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03797715108659291</v>
+        <v>0.03755044152382219</v>
       </c>
       <c r="W90">
-        <v>0.2268449877737814</v>
+        <v>0.2269456058886828</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.153286839337353</v>
+        <v>0.1515645152998546</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2383275773306428</v>
+        <v>0.2402275773306428</v>
       </c>
       <c r="C91">
-        <v>-1727.959365943014</v>
+        <v>-1758.196498969117</v>
       </c>
       <c r="D91">
-        <v>404.6276340569863</v>
+        <v>400.6735010308832</v>
       </c>
       <c r="E91">
-        <v>2299.887</v>
+        <v>2326.17</v>
       </c>
       <c r="F91">
-        <v>2339.187</v>
+        <v>2365.47</v>
       </c>
       <c r="G91">
         <v>206.6</v>
@@ -8749,37 +8749,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M91">
-        <v>551.5802946000001</v>
+        <v>557.7778260000001</v>
       </c>
       <c r="N91">
-        <v>-467.9802946000001</v>
+        <v>-474.1778260000001</v>
       </c>
       <c r="O91">
-        <v>-115.9431457416817</v>
+        <v>-117.4785977567351</v>
       </c>
       <c r="P91">
-        <v>-352.0371488583184</v>
+        <v>-356.699228243265</v>
       </c>
       <c r="Q91">
-        <v>-261.3371488583184</v>
+        <v>-265.999228243265</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3304180735428647</v>
+        <v>0.3588798808971512</v>
       </c>
       <c r="T91">
-        <v>6.573165670735905</v>
+        <v>7.230482237809497</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03755044152382219</v>
+        <v>0.03713321439577972</v>
       </c>
       <c r="W91">
-        <v>0.2269456058886828</v>
+        <v>0.2270439880454752</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1515645152998546</v>
+        <v>0.1498804651298562</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2402275773306428</v>
+        <v>0.2421275773306427</v>
       </c>
       <c r="C92">
-        <v>-1758.196498969117</v>
+        <v>-1788.357098144482</v>
       </c>
       <c r="D92">
-        <v>400.6735010308832</v>
+        <v>396.7959018555183</v>
       </c>
       <c r="E92">
-        <v>2326.17</v>
+        <v>2352.453</v>
       </c>
       <c r="F92">
-        <v>2365.47</v>
+        <v>2391.753</v>
       </c>
       <c r="G92">
         <v>206.6</v>
@@ -8831,37 +8831,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M92">
-        <v>557.7778260000001</v>
+        <v>563.9753574</v>
       </c>
       <c r="N92">
-        <v>-474.1778260000001</v>
+        <v>-480.3753574</v>
       </c>
       <c r="O92">
-        <v>-117.4785977567351</v>
+        <v>-119.0140497717885</v>
       </c>
       <c r="P92">
-        <v>-356.699228243265</v>
+        <v>-361.3613076282115</v>
       </c>
       <c r="Q92">
-        <v>-265.999228243265</v>
+        <v>-270.6613076282115</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3588798808971512</v>
+        <v>0.393666534330168</v>
       </c>
       <c r="T92">
-        <v>7.230482237809497</v>
+        <v>8.033869153121664</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03713321439577972</v>
+        <v>0.0367251570947272</v>
       </c>
       <c r="W92">
-        <v>0.2270439880454752</v>
+        <v>0.2271402079570633</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1498804651298562</v>
+        <v>0.1482334270515062</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2421275773306427</v>
+        <v>0.2440275773306428</v>
       </c>
       <c r="C93">
-        <v>-1788.357098144482</v>
+        <v>-1818.443364186865</v>
       </c>
       <c r="D93">
-        <v>396.7959018555183</v>
+        <v>392.9926358131356</v>
       </c>
       <c r="E93">
-        <v>2352.453</v>
+        <v>2378.736</v>
       </c>
       <c r="F93">
-        <v>2391.753</v>
+        <v>2418.036</v>
       </c>
       <c r="G93">
         <v>206.6</v>
@@ -8913,37 +8913,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M93">
-        <v>563.9753574</v>
+        <v>570.1728888</v>
       </c>
       <c r="N93">
-        <v>-480.3753574</v>
+        <v>-486.5728888</v>
       </c>
       <c r="O93">
-        <v>-119.0140497717885</v>
+        <v>-120.5495017868418</v>
       </c>
       <c r="P93">
-        <v>-361.3613076282115</v>
+        <v>-366.0233870131581</v>
       </c>
       <c r="Q93">
-        <v>-270.6613076282115</v>
+        <v>-275.3233870131581</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.393666534330168</v>
+        <v>0.4371498511214392</v>
       </c>
       <c r="T93">
-        <v>8.033869153121664</v>
+        <v>9.038102797261875</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0367251570947272</v>
+        <v>0.03632597060456713</v>
       </c>
       <c r="W93">
-        <v>0.2271402079570633</v>
+        <v>0.2272343361314431</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1482334270515062</v>
+        <v>0.1466221941487724</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2440275773306428</v>
+        <v>0.2459275773306427</v>
       </c>
       <c r="C94">
-        <v>-1818.443364186865</v>
+        <v>-1848.457414240058</v>
       </c>
       <c r="D94">
-        <v>392.9926358131356</v>
+        <v>389.2615857599419</v>
       </c>
       <c r="E94">
-        <v>2378.736</v>
+        <v>2405.019</v>
       </c>
       <c r="F94">
-        <v>2418.036</v>
+        <v>2444.319</v>
       </c>
       <c r="G94">
         <v>206.6</v>
@@ -8995,37 +8995,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M94">
-        <v>570.1728888</v>
+        <v>576.3704202000001</v>
       </c>
       <c r="N94">
-        <v>-486.5728888</v>
+        <v>-492.7704202000001</v>
       </c>
       <c r="O94">
-        <v>-120.5495017868418</v>
+        <v>-122.0849538018953</v>
       </c>
       <c r="P94">
-        <v>-366.0233870131581</v>
+        <v>-370.6854663981048</v>
       </c>
       <c r="Q94">
-        <v>-275.3233870131581</v>
+        <v>-279.9854663981048</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4371498511214392</v>
+        <v>0.4930569727102161</v>
       </c>
       <c r="T94">
-        <v>9.038102797261875</v>
+        <v>10.32926033972786</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03632597060456713</v>
+        <v>0.03593536877010941</v>
       </c>
       <c r="W94">
-        <v>0.2272343361314431</v>
+        <v>0.2273264400440082</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1466221941487724</v>
+        <v>0.1450456114159899</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2459275773306427</v>
+        <v>0.2478275773306428</v>
       </c>
       <c r="C95">
-        <v>-1848.457414240058</v>
+        <v>-1878.401285803812</v>
       </c>
       <c r="D95">
-        <v>389.2615857599419</v>
+        <v>385.6007141961878</v>
       </c>
       <c r="E95">
-        <v>2405.019</v>
+        <v>2431.302</v>
       </c>
       <c r="F95">
-        <v>2444.319</v>
+        <v>2470.602</v>
       </c>
       <c r="G95">
         <v>206.6</v>
@@ -9077,37 +9077,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M95">
-        <v>576.3704202000001</v>
+        <v>582.5679516000001</v>
       </c>
       <c r="N95">
-        <v>-492.7704202000001</v>
+        <v>-498.9679516000001</v>
       </c>
       <c r="O95">
-        <v>-122.0849538018953</v>
+        <v>-123.6204058169487</v>
       </c>
       <c r="P95">
-        <v>-370.6854663981048</v>
+        <v>-375.3475457830514</v>
       </c>
       <c r="Q95">
-        <v>-279.9854663981048</v>
+        <v>-284.6475457830514</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4930569727102161</v>
+        <v>0.5675998014952522</v>
       </c>
       <c r="T95">
-        <v>10.32926033972786</v>
+        <v>12.0508037296825</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03593536877010941</v>
+        <v>0.03555307761298059</v>
       </c>
       <c r="W95">
-        <v>0.2273264400440082</v>
+        <v>0.2274165842988592</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1450456114159899</v>
+        <v>0.1435025729966708</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2478275773306428</v>
+        <v>0.2497275773306428</v>
       </c>
       <c r="C96">
-        <v>-1878.401285803812</v>
+        <v>-1908.276940444067</v>
       </c>
       <c r="D96">
-        <v>385.6007141961878</v>
+        <v>382.0080595559334</v>
       </c>
       <c r="E96">
-        <v>2431.302</v>
+        <v>2457.585</v>
       </c>
       <c r="F96">
-        <v>2470.602</v>
+        <v>2496.885</v>
       </c>
       <c r="G96">
         <v>206.6</v>
@@ -9159,37 +9159,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M96">
-        <v>582.5679516000001</v>
+        <v>588.7654830000001</v>
       </c>
       <c r="N96">
-        <v>-498.9679516000001</v>
+        <v>-505.1654830000001</v>
       </c>
       <c r="O96">
-        <v>-123.6204058169487</v>
+        <v>-125.155857832002</v>
       </c>
       <c r="P96">
-        <v>-375.3475457830514</v>
+        <v>-380.0096251679981</v>
       </c>
       <c r="Q96">
-        <v>-284.6475457830514</v>
+        <v>-289.3096251679981</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5675998014952522</v>
+        <v>0.6719597617943032</v>
       </c>
       <c r="T96">
-        <v>12.0508037296825</v>
+        <v>14.46096447561901</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03555307761298059</v>
+        <v>0.03517883469073868</v>
       </c>
       <c r="W96">
-        <v>0.2274165842988592</v>
+        <v>0.2275048307799238</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1435025729966708</v>
+        <v>0.1419920195967059</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2497275773306428</v>
+        <v>0.2516275773306428</v>
       </c>
       <c r="C97">
-        <v>-1908.276940444067</v>
+        <v>-1938.086267297685</v>
       </c>
       <c r="D97">
-        <v>382.0080595559334</v>
+        <v>378.4817327023151</v>
       </c>
       <c r="E97">
-        <v>2457.585</v>
+        <v>2483.868</v>
       </c>
       <c r="F97">
-        <v>2496.885</v>
+        <v>2523.168000000001</v>
       </c>
       <c r="G97">
         <v>206.6</v>
@@ -9241,37 +9241,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M97">
-        <v>588.7654830000001</v>
+        <v>594.9630144000001</v>
       </c>
       <c r="N97">
-        <v>-505.1654830000001</v>
+        <v>-511.3630144000001</v>
       </c>
       <c r="O97">
-        <v>-125.155857832002</v>
+        <v>-126.6913098470554</v>
       </c>
       <c r="P97">
-        <v>-380.0096251679981</v>
+        <v>-384.6717045529447</v>
       </c>
       <c r="Q97">
-        <v>-289.3096251679981</v>
+        <v>-293.9717045529447</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6719597617943032</v>
+        <v>0.8284997022428792</v>
       </c>
       <c r="T97">
-        <v>14.46096447561901</v>
+        <v>18.07620559452377</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03517883469073868</v>
+        <v>0.03481238849604349</v>
       </c>
       <c r="W97">
-        <v>0.2275048307799238</v>
+        <v>0.227591238792633</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1419920195967059</v>
+        <v>0.1405129360592402</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2516275773306427</v>
+        <v>0.2535275773306427</v>
       </c>
       <c r="C98">
-        <v>-1938.086267297685</v>
+        <v>-1967.831086384853</v>
       </c>
       <c r="D98">
-        <v>378.4817327023151</v>
+        <v>375.0199136151469</v>
       </c>
       <c r="E98">
-        <v>2483.868</v>
+        <v>2510.151</v>
       </c>
       <c r="F98">
-        <v>2523.168</v>
+        <v>2549.451</v>
       </c>
       <c r="G98">
         <v>206.6</v>
@@ -9323,37 +9323,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M98">
-        <v>594.9630144</v>
+        <v>601.1605458</v>
       </c>
       <c r="N98">
-        <v>-511.3630144</v>
+        <v>-517.5605458</v>
       </c>
       <c r="O98">
-        <v>-126.6913098470554</v>
+        <v>-128.2267618621088</v>
       </c>
       <c r="P98">
-        <v>-384.6717045529446</v>
+        <v>-389.3337839378912</v>
       </c>
       <c r="Q98">
-        <v>-293.9717045529446</v>
+        <v>-298.6337839378912</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8284997022428771</v>
+        <v>1.089399602990503</v>
       </c>
       <c r="T98">
-        <v>18.07620559452372</v>
+        <v>24.10160745936497</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0348123884960435</v>
+        <v>0.0344534978929915</v>
       </c>
       <c r="W98">
-        <v>0.227591238792633</v>
+        <v>0.2276758651968326</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1405129360592402</v>
+        <v>0.1390643490895573</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2535275773306427</v>
+        <v>0.2554275773306428</v>
       </c>
       <c r="C99">
-        <v>-1967.831086384853</v>
+        <v>-1997.51315174134</v>
       </c>
       <c r="D99">
-        <v>375.0199136151469</v>
+        <v>371.6208482586603</v>
       </c>
       <c r="E99">
-        <v>2510.151</v>
+        <v>2536.434</v>
       </c>
       <c r="F99">
-        <v>2549.451</v>
+        <v>2575.734</v>
       </c>
       <c r="G99">
         <v>206.6</v>
@@ -9405,37 +9405,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M99">
-        <v>601.1605458</v>
+        <v>607.3580772</v>
       </c>
       <c r="N99">
-        <v>-517.5605458</v>
+        <v>-523.7580772</v>
       </c>
       <c r="O99">
-        <v>-128.2267618621088</v>
+        <v>-129.7622138771622</v>
       </c>
       <c r="P99">
-        <v>-389.3337839378912</v>
+        <v>-393.9958633228378</v>
       </c>
       <c r="Q99">
-        <v>-298.6337839378912</v>
+        <v>-303.2958633228378</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.089399602990503</v>
+        <v>1.611199404485754</v>
       </c>
       <c r="T99">
-        <v>24.10160745936497</v>
+        <v>36.15241118904745</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0344534978929915</v>
+        <v>0.03410193158796097</v>
       </c>
       <c r="W99">
-        <v>0.2276758651968326</v>
+        <v>0.2277587645315588</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1390643490895573</v>
+        <v>0.1376453251192558</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2554275773306428</v>
+        <v>0.2573275773306428</v>
       </c>
       <c r="C100">
-        <v>-1997.51315174134</v>
+        <v>-2027.134154381949</v>
       </c>
       <c r="D100">
-        <v>371.6208482586603</v>
+        <v>368.2828456180508</v>
       </c>
       <c r="E100">
-        <v>2536.434</v>
+        <v>2562.717</v>
       </c>
       <c r="F100">
-        <v>2575.734</v>
+        <v>2602.017</v>
       </c>
       <c r="G100">
         <v>206.6</v>
@@ -9487,37 +9487,37 @@
         <v>83.60000000000001</v>
       </c>
       <c r="M100">
-        <v>607.3580772</v>
+        <v>613.5556086000001</v>
       </c>
       <c r="N100">
-        <v>-523.7580772</v>
+        <v>-529.9556086000001</v>
       </c>
       <c r="O100">
-        <v>-129.7622138771622</v>
+        <v>-131.2976658922156</v>
       </c>
       <c r="P100">
-        <v>-393.9958633228378</v>
+        <v>-398.6579427077845</v>
       </c>
       <c r="Q100">
-        <v>-303.2958633228378</v>
+        <v>-307.9579427077845</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.611199404485754</v>
+        <v>3.176598808971509</v>
       </c>
       <c r="T100">
-        <v>36.15241118904745</v>
+        <v>72.3048223780949</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03410193158796097</v>
+        <v>0.03375746763252702</v>
       </c>
       <c r="W100">
-        <v>0.2277587645315588</v>
+        <v>0.2278399891322501</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1376453251192558</v>
+        <v>0.1362549682998693</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2573275773306428</v>
-      </c>
-      <c r="C101">
-        <v>-2027.134154381949</v>
-      </c>
-      <c r="D101">
-        <v>368.2828456180508</v>
-      </c>
-      <c r="E101">
-        <v>2562.717</v>
-      </c>
-      <c r="F101">
-        <v>2602.017</v>
-      </c>
-      <c r="G101">
-        <v>206.6</v>
-      </c>
-      <c r="H101">
-        <v>2589</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>174.3</v>
-      </c>
-      <c r="K101">
-        <v>90.7</v>
-      </c>
-      <c r="L101">
-        <v>83.60000000000001</v>
-      </c>
-      <c r="M101">
-        <v>613.5556086000001</v>
-      </c>
-      <c r="N101">
-        <v>-529.9556086000001</v>
-      </c>
-      <c r="O101">
-        <v>-131.2976658922156</v>
-      </c>
-      <c r="P101">
-        <v>-398.6579427077845</v>
-      </c>
-      <c r="Q101">
-        <v>-307.9579427077845</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.176598808971509</v>
-      </c>
-      <c r="T101">
-        <v>72.3048223780949</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03375746763252702</v>
-      </c>
-      <c r="W101">
-        <v>0.2278399891322501</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1362549682998693</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
